--- a/data/LME_008/LME_008.xlsx
+++ b/data/LME_008/LME_008.xlsx
@@ -10,8 +10,12 @@
     <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Catch" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="SPPR" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="PPR" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="NPP" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="sppr_all" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="sppr_inner" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="sppr_PP" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Recycling" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="PPR" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="NPP" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,7 +25,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -36,13 +40,22 @@
       <b val="1"/>
       <sz val="14"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E79"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -57,7 +70,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -68,6 +81,13 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -434,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D82"/>
+  <dimension ref="A1:D85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -512,1035 +532,1066 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>catch years</t>
+          <t>model workbooks</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1950-2019</t>
+          <t>none yet</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>taxa in catch</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>160</v>
+          <t>catch years</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>1950-2019</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>taxa in catch</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>taxa with a trophic level</t>
         </is>
       </c>
-      <c r="B10" t="n">
+      <c r="B11" t="n">
         <v>92</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>year</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>catch_tonnes</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>ppr_tonnes</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>ppr_over_npp_percent</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>1950</v>
-      </c>
-      <c r="B13" t="n">
-        <v>404040.531</v>
-      </c>
-      <c r="C13" t="n">
-        <v>345179957.669</v>
-      </c>
-      <c r="D13" t="n">
-        <v>466.6925</v>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>model source context</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>No pilot model selected</t>
+        </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="n">
-        <v>1951</v>
-      </c>
-      <c r="B14" t="n">
-        <v>355513.761</v>
-      </c>
-      <c r="C14" t="n">
-        <v>297671073.256</v>
-      </c>
-      <c r="D14" t="n">
-        <v>402.4592</v>
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>year</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>catch_tonnes</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>ppr_tonnes</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>ppr_over_npp_percent</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1952</v>
+        <v>1950</v>
       </c>
       <c r="B15" t="n">
-        <v>450768.636</v>
+        <v>404040.531</v>
       </c>
       <c r="C15" t="n">
-        <v>395274102.396</v>
+        <v>345179957.669</v>
       </c>
       <c r="D15" t="n">
-        <v>534.4211</v>
+        <v>51.8547</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>1953</v>
+        <v>1951</v>
       </c>
       <c r="B16" t="n">
-        <v>443005.997</v>
+        <v>355513.761</v>
       </c>
       <c r="C16" t="n">
-        <v>401227920.35</v>
+        <v>297671073.256</v>
       </c>
       <c r="D16" t="n">
-        <v>542.4708000000001</v>
+        <v>44.7177</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>1954</v>
+        <v>1952</v>
       </c>
       <c r="B17" t="n">
-        <v>571545.8100000001</v>
+        <v>450768.636</v>
       </c>
       <c r="C17" t="n">
-        <v>560986351.207</v>
+        <v>395274102.396</v>
       </c>
       <c r="D17" t="n">
-        <v>758.4684999999999</v>
+        <v>59.3801</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>1955</v>
+        <v>1953</v>
       </c>
       <c r="B18" t="n">
-        <v>630579.654</v>
+        <v>443005.997</v>
       </c>
       <c r="C18" t="n">
-        <v>626279686.074</v>
+        <v>401227920.35</v>
       </c>
       <c r="D18" t="n">
-        <v>846.7468</v>
+        <v>60.2745</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>1956</v>
+        <v>1954</v>
       </c>
       <c r="B19" t="n">
-        <v>664664.474</v>
+        <v>571545.8100000001</v>
       </c>
       <c r="C19" t="n">
-        <v>665084006.7130001</v>
+        <v>560986351.207</v>
       </c>
       <c r="D19" t="n">
-        <v>899.2113000000001</v>
+        <v>84.2743</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>1957</v>
+        <v>1955</v>
       </c>
       <c r="B20" t="n">
-        <v>659134.785</v>
+        <v>630579.654</v>
       </c>
       <c r="C20" t="n">
-        <v>656136086.694</v>
+        <v>626279686.074</v>
       </c>
       <c r="D20" t="n">
-        <v>887.1135</v>
+        <v>94.083</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>1958</v>
+        <v>1956</v>
       </c>
       <c r="B21" t="n">
-        <v>579857.067</v>
+        <v>664664.474</v>
       </c>
       <c r="C21" t="n">
-        <v>549947814.477</v>
+        <v>665084006.7130001</v>
       </c>
       <c r="D21" t="n">
-        <v>743.5441</v>
+        <v>99.91240000000001</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>1959</v>
+        <v>1957</v>
       </c>
       <c r="B22" t="n">
-        <v>646932.557</v>
+        <v>659134.785</v>
       </c>
       <c r="C22" t="n">
-        <v>621436636.198</v>
+        <v>656136086.694</v>
       </c>
       <c r="D22" t="n">
-        <v>840.1989</v>
+        <v>98.5682</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>1960</v>
+        <v>1958</v>
       </c>
       <c r="B23" t="n">
-        <v>720258.095</v>
+        <v>579857.067</v>
       </c>
       <c r="C23" t="n">
-        <v>691608952.192</v>
+        <v>549947814.477</v>
       </c>
       <c r="D23" t="n">
-        <v>935.0737</v>
+        <v>82.616</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>1961</v>
+        <v>1959</v>
       </c>
       <c r="B24" t="n">
-        <v>806456.9840000001</v>
+        <v>646932.557</v>
       </c>
       <c r="C24" t="n">
-        <v>781119914.531</v>
+        <v>621436636.198</v>
       </c>
       <c r="D24" t="n">
-        <v>1056.0949</v>
+        <v>93.3554</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>1962</v>
+        <v>1960</v>
       </c>
       <c r="B25" t="n">
-        <v>888523.853</v>
+        <v>720258.095</v>
       </c>
       <c r="C25" t="n">
-        <v>859774208.8329999</v>
+        <v>691608952.192</v>
       </c>
       <c r="D25" t="n">
-        <v>1162.4376</v>
+        <v>103.8971</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>1963</v>
+        <v>1961</v>
       </c>
       <c r="B26" t="n">
-        <v>1433466.843</v>
+        <v>806456.9840000001</v>
       </c>
       <c r="C26" t="n">
-        <v>1604840555.048</v>
+        <v>781119914.531</v>
       </c>
       <c r="D26" t="n">
-        <v>2169.7872</v>
+        <v>117.3439</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>1964</v>
+        <v>1962</v>
       </c>
       <c r="B27" t="n">
-        <v>1145116.937</v>
+        <v>888523.853</v>
       </c>
       <c r="C27" t="n">
-        <v>1204635194.365</v>
+        <v>859774208.8329999</v>
       </c>
       <c r="D27" t="n">
-        <v>1628.6989</v>
+        <v>129.1597</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>1965</v>
+        <v>1963</v>
       </c>
       <c r="B28" t="n">
-        <v>1233386.733</v>
+        <v>1433466.843</v>
       </c>
       <c r="C28" t="n">
-        <v>1242806854.873</v>
+        <v>1604840555.048</v>
       </c>
       <c r="D28" t="n">
-        <v>1680.308</v>
+        <v>241.0875</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>1966</v>
+        <v>1964</v>
       </c>
       <c r="B29" t="n">
-        <v>1019445.11</v>
+        <v>1145116.937</v>
       </c>
       <c r="C29" t="n">
-        <v>927815976.5140001</v>
+        <v>1204635194.365</v>
       </c>
       <c r="D29" t="n">
-        <v>1254.4319</v>
+        <v>180.9665</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>1967</v>
+        <v>1965</v>
       </c>
       <c r="B30" t="n">
-        <v>811934.037</v>
+        <v>1233386.733</v>
       </c>
       <c r="C30" t="n">
-        <v>662039550.043</v>
+        <v>1242806854.873</v>
       </c>
       <c r="D30" t="n">
-        <v>895.0951</v>
+        <v>186.7009</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>1968</v>
+        <v>1966</v>
       </c>
       <c r="B31" t="n">
-        <v>1105394.821</v>
+        <v>1019445.11</v>
       </c>
       <c r="C31" t="n">
-        <v>859020803.538</v>
+        <v>927815976.5140001</v>
       </c>
       <c r="D31" t="n">
-        <v>1161.419</v>
+        <v>139.3813</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>1969</v>
+        <v>1967</v>
       </c>
       <c r="B32" t="n">
-        <v>1228105.677</v>
+        <v>811934.037</v>
       </c>
       <c r="C32" t="n">
-        <v>875235031.368</v>
+        <v>662039550.043</v>
       </c>
       <c r="D32" t="n">
-        <v>1183.3411</v>
+        <v>99.455</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>1970</v>
+        <v>1968</v>
       </c>
       <c r="B33" t="n">
-        <v>1534739.847</v>
+        <v>1105394.821</v>
       </c>
       <c r="C33" t="n">
-        <v>1346845892.899</v>
+        <v>859020803.538</v>
       </c>
       <c r="D33" t="n">
-        <v>1820.9715</v>
+        <v>129.0466</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>1971</v>
+        <v>1969</v>
       </c>
       <c r="B34" t="n">
-        <v>1399952.916</v>
+        <v>1228105.677</v>
       </c>
       <c r="C34" t="n">
-        <v>1172721106.567</v>
+        <v>875235031.368</v>
       </c>
       <c r="D34" t="n">
-        <v>1585.5502</v>
+        <v>131.4823</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>1972</v>
+        <v>1970</v>
       </c>
       <c r="B35" t="n">
-        <v>1085749.785</v>
+        <v>1534739.847</v>
       </c>
       <c r="C35" t="n">
-        <v>947703078.6569999</v>
+        <v>1346845892.899</v>
       </c>
       <c r="D35" t="n">
-        <v>1281.3198</v>
+        <v>202.3302</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>1973</v>
+        <v>1971</v>
       </c>
       <c r="B36" t="n">
-        <v>1414617.18</v>
+        <v>1399952.916</v>
       </c>
       <c r="C36" t="n">
-        <v>1532566083.31</v>
+        <v>1172721106.567</v>
       </c>
       <c r="D36" t="n">
-        <v>2072.0701</v>
+        <v>176.1722</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>1974</v>
+        <v>1972</v>
       </c>
       <c r="B37" t="n">
-        <v>909884.603</v>
+        <v>1085749.785</v>
       </c>
       <c r="C37" t="n">
-        <v>791522397.742</v>
+        <v>947703078.6569999</v>
       </c>
       <c r="D37" t="n">
-        <v>1070.1594</v>
+        <v>142.3689</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="B38" t="n">
-        <v>858536.463</v>
+        <v>1414617.18</v>
       </c>
       <c r="C38" t="n">
-        <v>766445476.97</v>
+        <v>1532566083.31</v>
       </c>
       <c r="D38" t="n">
-        <v>1036.2547</v>
+        <v>230.23</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>1976</v>
+        <v>1974</v>
       </c>
       <c r="B39" t="n">
-        <v>674712.238</v>
+        <v>909884.603</v>
       </c>
       <c r="C39" t="n">
-        <v>603946868.434</v>
+        <v>791522397.742</v>
       </c>
       <c r="D39" t="n">
-        <v>816.5522</v>
+        <v>118.9066</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>1977</v>
+        <v>1975</v>
       </c>
       <c r="B40" t="n">
-        <v>454420.972</v>
+        <v>858536.463</v>
       </c>
       <c r="C40" t="n">
-        <v>349355754.453</v>
+        <v>766445476.97</v>
       </c>
       <c r="D40" t="n">
-        <v>472.3383</v>
+        <v>115.1394</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>1978</v>
+        <v>1976</v>
       </c>
       <c r="B41" t="n">
-        <v>497695.274</v>
+        <v>674712.238</v>
       </c>
       <c r="C41" t="n">
-        <v>398129864.232</v>
+        <v>603946868.434</v>
       </c>
       <c r="D41" t="n">
-        <v>538.2822</v>
+        <v>90.72799999999999</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>1979</v>
+        <v>1977</v>
       </c>
       <c r="B42" t="n">
-        <v>489960.734</v>
+        <v>454420.972</v>
       </c>
       <c r="C42" t="n">
-        <v>431773609.507</v>
+        <v>349355754.453</v>
       </c>
       <c r="D42" t="n">
-        <v>583.7694</v>
+        <v>52.482</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>1980</v>
+        <v>1978</v>
       </c>
       <c r="B43" t="n">
-        <v>500605.48</v>
+        <v>497695.274</v>
       </c>
       <c r="C43" t="n">
-        <v>431950123.476</v>
+        <v>398129864.232</v>
       </c>
       <c r="D43" t="n">
-        <v>584.0081</v>
+        <v>59.8091</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>1981</v>
+        <v>1979</v>
       </c>
       <c r="B44" t="n">
-        <v>509627.927</v>
+        <v>489960.734</v>
       </c>
       <c r="C44" t="n">
-        <v>456718672.419</v>
+        <v>431773609.507</v>
       </c>
       <c r="D44" t="n">
-        <v>617.4958</v>
+        <v>64.8633</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>1982</v>
+        <v>1980</v>
       </c>
       <c r="B45" t="n">
-        <v>498282.979</v>
+        <v>500605.48</v>
       </c>
       <c r="C45" t="n">
-        <v>445595756.733</v>
+        <v>431950123.476</v>
       </c>
       <c r="D45" t="n">
-        <v>602.4573</v>
+        <v>64.88979999999999</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>1983</v>
+        <v>1981</v>
       </c>
       <c r="B46" t="n">
-        <v>446677.642</v>
+        <v>509627.927</v>
       </c>
       <c r="C46" t="n">
-        <v>377064765.588</v>
+        <v>456718672.419</v>
       </c>
       <c r="D46" t="n">
-        <v>509.8016</v>
+        <v>68.61060000000001</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>1984</v>
+        <v>1982</v>
       </c>
       <c r="B47" t="n">
-        <v>480264.602</v>
+        <v>498282.979</v>
       </c>
       <c r="C47" t="n">
-        <v>456471677.769</v>
+        <v>445595756.733</v>
       </c>
       <c r="D47" t="n">
-        <v>617.1618999999999</v>
+        <v>66.9397</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>1985</v>
+        <v>1983</v>
       </c>
       <c r="B48" t="n">
-        <v>534494.306</v>
+        <v>446677.642</v>
       </c>
       <c r="C48" t="n">
-        <v>481447438.292</v>
+        <v>377064765.588</v>
       </c>
       <c r="D48" t="n">
-        <v>650.9298</v>
+        <v>56.6446</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>1986</v>
+        <v>1984</v>
       </c>
       <c r="B49" t="n">
-        <v>581460.259</v>
+        <v>480264.602</v>
       </c>
       <c r="C49" t="n">
-        <v>530110767.605</v>
+        <v>456471677.769</v>
       </c>
       <c r="D49" t="n">
-        <v>716.7239</v>
+        <v>68.5735</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>1987</v>
+        <v>1985</v>
       </c>
       <c r="B50" t="n">
-        <v>566150.226</v>
+        <v>534494.306</v>
       </c>
       <c r="C50" t="n">
-        <v>449091976.679</v>
+        <v>481447438.292</v>
       </c>
       <c r="D50" t="n">
-        <v>607.1843</v>
+        <v>72.32550000000001</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>1988</v>
+        <v>1986</v>
       </c>
       <c r="B51" t="n">
-        <v>585924.905</v>
+        <v>581460.259</v>
       </c>
       <c r="C51" t="n">
-        <v>482573452.172</v>
+        <v>530110767.605</v>
       </c>
       <c r="D51" t="n">
-        <v>652.4521999999999</v>
+        <v>79.636</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>1989</v>
+        <v>1987</v>
       </c>
       <c r="B52" t="n">
-        <v>580334.314</v>
+        <v>566150.226</v>
       </c>
       <c r="C52" t="n">
-        <v>504508745.923</v>
+        <v>449091976.679</v>
       </c>
       <c r="D52" t="n">
-        <v>682.1093</v>
+        <v>67.4649</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>1990</v>
+        <v>1988</v>
       </c>
       <c r="B53" t="n">
-        <v>587179.961</v>
+        <v>585924.905</v>
       </c>
       <c r="C53" t="n">
-        <v>443975388.959</v>
+        <v>482573452.172</v>
       </c>
       <c r="D53" t="n">
-        <v>600.2665</v>
+        <v>72.49469999999999</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>1991</v>
+        <v>1989</v>
       </c>
       <c r="B54" t="n">
-        <v>512197.204</v>
+        <v>580334.314</v>
       </c>
       <c r="C54" t="n">
-        <v>391677998</v>
+        <v>504508745.923</v>
       </c>
       <c r="D54" t="n">
-        <v>529.5590999999999</v>
+        <v>75.7899</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>1992</v>
+        <v>1990</v>
       </c>
       <c r="B55" t="n">
-        <v>478483.516</v>
+        <v>587179.961</v>
       </c>
       <c r="C55" t="n">
-        <v>324809053.574</v>
+        <v>443975388.959</v>
       </c>
       <c r="D55" t="n">
-        <v>439.1505</v>
+        <v>66.69629999999999</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>1993</v>
+        <v>1991</v>
       </c>
       <c r="B56" t="n">
-        <v>370094.562</v>
+        <v>512197.204</v>
       </c>
       <c r="C56" t="n">
-        <v>228683711.26</v>
+        <v>391677998</v>
       </c>
       <c r="D56" t="n">
-        <v>309.1865</v>
+        <v>58.8399</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>1994</v>
+        <v>1992</v>
       </c>
       <c r="B57" t="n">
-        <v>359629.566</v>
+        <v>478483.516</v>
       </c>
       <c r="C57" t="n">
-        <v>154725681.26</v>
+        <v>324809053.574</v>
       </c>
       <c r="D57" t="n">
-        <v>209.1932</v>
+        <v>48.7945</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>1995</v>
+        <v>1993</v>
       </c>
       <c r="B58" t="n">
-        <v>331790.627</v>
+        <v>370094.562</v>
       </c>
       <c r="C58" t="n">
-        <v>136567766.098</v>
+        <v>228683711.26</v>
       </c>
       <c r="D58" t="n">
-        <v>184.6433</v>
+        <v>34.3541</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>1996</v>
+        <v>1994</v>
       </c>
       <c r="B59" t="n">
-        <v>313994.367</v>
+        <v>359629.566</v>
       </c>
       <c r="C59" t="n">
-        <v>130360664.833</v>
+        <v>154725681.26</v>
       </c>
       <c r="D59" t="n">
-        <v>176.2511</v>
+        <v>23.2437</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>1997</v>
+        <v>1995</v>
       </c>
       <c r="B60" t="n">
-        <v>317751.817</v>
+        <v>331790.627</v>
       </c>
       <c r="C60" t="n">
-        <v>141541470.33</v>
+        <v>136567766.098</v>
       </c>
       <c r="D60" t="n">
-        <v>191.3678</v>
+        <v>20.5159</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>1998</v>
+        <v>1996</v>
       </c>
       <c r="B61" t="n">
-        <v>318171.12</v>
+        <v>313994.367</v>
       </c>
       <c r="C61" t="n">
-        <v>143149946.218</v>
+        <v>130360664.833</v>
       </c>
       <c r="D61" t="n">
-        <v>193.5425</v>
+        <v>19.5835</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>1999</v>
+        <v>1997</v>
       </c>
       <c r="B62" t="n">
-        <v>338654.312</v>
+        <v>317751.817</v>
       </c>
       <c r="C62" t="n">
-        <v>146064001.255</v>
+        <v>141541470.33</v>
       </c>
       <c r="D62" t="n">
-        <v>197.4824</v>
+        <v>21.2631</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>2000</v>
+        <v>1998</v>
       </c>
       <c r="B63" t="n">
-        <v>343753.929</v>
+        <v>318171.12</v>
       </c>
       <c r="C63" t="n">
-        <v>143929384.909</v>
+        <v>143149946.218</v>
       </c>
       <c r="D63" t="n">
-        <v>194.5964</v>
+        <v>21.5047</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>2001</v>
+        <v>1999</v>
       </c>
       <c r="B64" t="n">
-        <v>342001.794</v>
+        <v>338654.312</v>
       </c>
       <c r="C64" t="n">
-        <v>149216500.134</v>
+        <v>146064001.255</v>
       </c>
       <c r="D64" t="n">
-        <v>201.7447</v>
+        <v>21.9425</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>2002</v>
+        <v>2000</v>
       </c>
       <c r="B65" t="n">
-        <v>347318.046</v>
+        <v>343753.929</v>
       </c>
       <c r="C65" t="n">
-        <v>152886522.297</v>
+        <v>143929384.909</v>
       </c>
       <c r="D65" t="n">
-        <v>206.7066</v>
+        <v>21.6218</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>2003</v>
+        <v>2001</v>
       </c>
       <c r="B66" t="n">
-        <v>328843.619</v>
+        <v>342001.794</v>
       </c>
       <c r="C66" t="n">
-        <v>131631444.562</v>
+        <v>149216500.134</v>
       </c>
       <c r="D66" t="n">
-        <v>177.9692</v>
+        <v>22.4161</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>2004</v>
+        <v>2002</v>
       </c>
       <c r="B67" t="n">
-        <v>335541.088</v>
+        <v>347318.046</v>
       </c>
       <c r="C67" t="n">
-        <v>143488976.546</v>
+        <v>152886522.297</v>
       </c>
       <c r="D67" t="n">
-        <v>194.0009</v>
+        <v>22.9674</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>2005</v>
+        <v>2003</v>
       </c>
       <c r="B68" t="n">
-        <v>309816.005</v>
+        <v>328843.619</v>
       </c>
       <c r="C68" t="n">
-        <v>132800935.217</v>
+        <v>131631444.562</v>
       </c>
       <c r="D68" t="n">
-        <v>179.5504</v>
+        <v>19.7744</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>2006</v>
+        <v>2004</v>
       </c>
       <c r="B69" t="n">
-        <v>300833.355</v>
+        <v>335541.088</v>
       </c>
       <c r="C69" t="n">
-        <v>137897357.524</v>
+        <v>143488976.546</v>
       </c>
       <c r="D69" t="n">
-        <v>186.4409</v>
+        <v>21.5557</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>2007</v>
+        <v>2005</v>
       </c>
       <c r="B70" t="n">
-        <v>292793.842</v>
+        <v>309816.005</v>
       </c>
       <c r="C70" t="n">
-        <v>132492765.435</v>
+        <v>132800935.217</v>
       </c>
       <c r="D70" t="n">
-        <v>179.1337</v>
+        <v>19.95</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>2008</v>
+        <v>2006</v>
       </c>
       <c r="B71" t="n">
-        <v>282523.252</v>
+        <v>300833.355</v>
       </c>
       <c r="C71" t="n">
-        <v>129439124.776</v>
+        <v>137897357.524</v>
       </c>
       <c r="D71" t="n">
-        <v>175.0051</v>
+        <v>20.7157</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>2009</v>
+        <v>2007</v>
       </c>
       <c r="B72" t="n">
-        <v>279356.707</v>
+        <v>292793.842</v>
       </c>
       <c r="C72" t="n">
-        <v>127106994.123</v>
+        <v>132492765.435</v>
       </c>
       <c r="D72" t="n">
-        <v>171.852</v>
+        <v>19.9037</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>2010</v>
+        <v>2008</v>
       </c>
       <c r="B73" t="n">
-        <v>266265.773</v>
+        <v>282523.252</v>
       </c>
       <c r="C73" t="n">
-        <v>127945190.884</v>
+        <v>129439124.776</v>
       </c>
       <c r="D73" t="n">
-        <v>172.9853</v>
+        <v>19.445</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>2011</v>
+        <v>2009</v>
       </c>
       <c r="B74" t="n">
-        <v>204111.532</v>
+        <v>279356.707</v>
       </c>
       <c r="C74" t="n">
-        <v>104644625.857</v>
+        <v>127106994.123</v>
       </c>
       <c r="D74" t="n">
-        <v>141.4823</v>
+        <v>19.0947</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="B75" t="n">
-        <v>240837.716</v>
+        <v>266265.773</v>
       </c>
       <c r="C75" t="n">
-        <v>126687471.483</v>
+        <v>127945190.884</v>
       </c>
       <c r="D75" t="n">
-        <v>171.2848</v>
+        <v>19.2206</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>2013</v>
+        <v>2011</v>
       </c>
       <c r="B76" t="n">
-        <v>254210.921</v>
+        <v>204111.532</v>
       </c>
       <c r="C76" t="n">
-        <v>126654210.666</v>
+        <v>104644625.857</v>
       </c>
       <c r="D76" t="n">
-        <v>171.2399</v>
+        <v>15.7203</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="B77" t="n">
-        <v>244226.712</v>
+        <v>240837.716</v>
       </c>
       <c r="C77" t="n">
-        <v>118975599.784</v>
+        <v>126687471.483</v>
       </c>
       <c r="D77" t="n">
-        <v>160.8582</v>
+        <v>19.0316</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>2015</v>
+        <v>2013</v>
       </c>
       <c r="B78" t="n">
-        <v>266929.956</v>
+        <v>254210.921</v>
       </c>
       <c r="C78" t="n">
-        <v>124438119.884</v>
+        <v>126654210.666</v>
       </c>
       <c r="D78" t="n">
-        <v>168.2437</v>
+        <v>19.0267</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="B79" t="n">
-        <v>255999.158</v>
+        <v>244226.712</v>
       </c>
       <c r="C79" t="n">
-        <v>119195190.57</v>
+        <v>118975599.784</v>
       </c>
       <c r="D79" t="n">
-        <v>161.1551</v>
+        <v>17.8731</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>2017</v>
+        <v>2015</v>
       </c>
       <c r="B80" t="n">
-        <v>105782.702</v>
+        <v>266929.956</v>
       </c>
       <c r="C80" t="n">
-        <v>69000049.059</v>
+        <v>124438119.884</v>
       </c>
       <c r="D80" t="n">
-        <v>93.2899</v>
+        <v>18.6937</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>2018</v>
+        <v>2016</v>
       </c>
       <c r="B81" t="n">
-        <v>171053.375</v>
+        <v>255999.158</v>
       </c>
       <c r="C81" t="n">
-        <v>86145416.802</v>
+        <v>119195190.57</v>
       </c>
       <c r="D81" t="n">
-        <v>116.4709</v>
+        <v>17.9061</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
+        <v>2017</v>
+      </c>
+      <c r="B82" t="n">
+        <v>105782.702</v>
+      </c>
+      <c r="C82" t="n">
+        <v>69000049.059</v>
+      </c>
+      <c r="D82" t="n">
+        <v>10.3655</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B83" t="n">
+        <v>171053.375</v>
+      </c>
+      <c r="C83" t="n">
+        <v>86145416.802</v>
+      </c>
+      <c r="D83" t="n">
+        <v>12.9412</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
         <v>2019</v>
       </c>
-      <c r="B82" t="n">
+      <c r="B84" t="n">
         <v>148680.261</v>
       </c>
-      <c r="C82" t="n">
+      <c r="C84" t="n">
         <v>75212513.43099999</v>
       </c>
-      <c r="D82" t="n">
-        <v>101.6893</v>
+      <c r="D84" t="n">
+        <v>11.2988</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>PPR/NPP converts wet-weight PP to carbon at 9:1; NPP is the fixed 2019 ensemble median.</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1654,355 +1705,215 @@
           <t>commercial_group</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>1950</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
-        <is>
-          <t>1951</t>
-        </is>
-      </c>
-      <c r="G1" s="2" t="inlineStr">
-        <is>
-          <t>1952</t>
-        </is>
-      </c>
-      <c r="H1" s="2" t="inlineStr">
-        <is>
-          <t>1953</t>
-        </is>
-      </c>
-      <c r="I1" s="2" t="inlineStr">
-        <is>
-          <t>1954</t>
-        </is>
-      </c>
-      <c r="J1" s="2" t="inlineStr">
-        <is>
-          <t>1955</t>
-        </is>
-      </c>
-      <c r="K1" s="2" t="inlineStr">
-        <is>
-          <t>1956</t>
-        </is>
-      </c>
-      <c r="L1" s="2" t="inlineStr">
-        <is>
-          <t>1957</t>
-        </is>
-      </c>
-      <c r="M1" s="2" t="inlineStr">
-        <is>
-          <t>1958</t>
-        </is>
-      </c>
-      <c r="N1" s="2" t="inlineStr">
-        <is>
-          <t>1959</t>
-        </is>
-      </c>
-      <c r="O1" s="2" t="inlineStr">
-        <is>
-          <t>1960</t>
-        </is>
-      </c>
-      <c r="P1" s="2" t="inlineStr">
-        <is>
-          <t>1961</t>
-        </is>
-      </c>
-      <c r="Q1" s="2" t="inlineStr">
-        <is>
-          <t>1962</t>
-        </is>
-      </c>
-      <c r="R1" s="2" t="inlineStr">
-        <is>
-          <t>1963</t>
-        </is>
-      </c>
-      <c r="S1" s="2" t="inlineStr">
-        <is>
-          <t>1964</t>
-        </is>
-      </c>
-      <c r="T1" s="2" t="inlineStr">
-        <is>
-          <t>1965</t>
-        </is>
-      </c>
-      <c r="U1" s="2" t="inlineStr">
-        <is>
-          <t>1966</t>
-        </is>
-      </c>
-      <c r="V1" s="2" t="inlineStr">
-        <is>
-          <t>1967</t>
-        </is>
-      </c>
-      <c r="W1" s="2" t="inlineStr">
-        <is>
-          <t>1968</t>
-        </is>
-      </c>
-      <c r="X1" s="2" t="inlineStr">
-        <is>
-          <t>1969</t>
-        </is>
-      </c>
-      <c r="Y1" s="2" t="inlineStr">
-        <is>
-          <t>1970</t>
-        </is>
-      </c>
-      <c r="Z1" s="2" t="inlineStr">
-        <is>
-          <t>1971</t>
-        </is>
-      </c>
-      <c r="AA1" s="2" t="inlineStr">
-        <is>
-          <t>1972</t>
-        </is>
-      </c>
-      <c r="AB1" s="2" t="inlineStr">
-        <is>
-          <t>1973</t>
-        </is>
-      </c>
-      <c r="AC1" s="2" t="inlineStr">
-        <is>
-          <t>1974</t>
-        </is>
-      </c>
-      <c r="AD1" s="2" t="inlineStr">
-        <is>
-          <t>1975</t>
-        </is>
-      </c>
-      <c r="AE1" s="2" t="inlineStr">
-        <is>
-          <t>1976</t>
-        </is>
-      </c>
-      <c r="AF1" s="2" t="inlineStr">
-        <is>
-          <t>1977</t>
-        </is>
-      </c>
-      <c r="AG1" s="2" t="inlineStr">
-        <is>
-          <t>1978</t>
-        </is>
-      </c>
-      <c r="AH1" s="2" t="inlineStr">
-        <is>
-          <t>1979</t>
-        </is>
-      </c>
-      <c r="AI1" s="2" t="inlineStr">
-        <is>
-          <t>1980</t>
-        </is>
-      </c>
-      <c r="AJ1" s="2" t="inlineStr">
-        <is>
-          <t>1981</t>
-        </is>
-      </c>
-      <c r="AK1" s="2" t="inlineStr">
-        <is>
-          <t>1982</t>
-        </is>
-      </c>
-      <c r="AL1" s="2" t="inlineStr">
-        <is>
-          <t>1983</t>
-        </is>
-      </c>
-      <c r="AM1" s="2" t="inlineStr">
-        <is>
-          <t>1984</t>
-        </is>
-      </c>
-      <c r="AN1" s="2" t="inlineStr">
-        <is>
-          <t>1985</t>
-        </is>
-      </c>
-      <c r="AO1" s="2" t="inlineStr">
-        <is>
-          <t>1986</t>
-        </is>
-      </c>
-      <c r="AP1" s="2" t="inlineStr">
-        <is>
-          <t>1987</t>
-        </is>
-      </c>
-      <c r="AQ1" s="2" t="inlineStr">
-        <is>
-          <t>1988</t>
-        </is>
-      </c>
-      <c r="AR1" s="2" t="inlineStr">
-        <is>
-          <t>1989</t>
-        </is>
-      </c>
-      <c r="AS1" s="2" t="inlineStr">
-        <is>
-          <t>1990</t>
-        </is>
-      </c>
-      <c r="AT1" s="2" t="inlineStr">
-        <is>
-          <t>1991</t>
-        </is>
-      </c>
-      <c r="AU1" s="2" t="inlineStr">
-        <is>
-          <t>1992</t>
-        </is>
-      </c>
-      <c r="AV1" s="2" t="inlineStr">
-        <is>
-          <t>1993</t>
-        </is>
-      </c>
-      <c r="AW1" s="2" t="inlineStr">
-        <is>
-          <t>1994</t>
-        </is>
-      </c>
-      <c r="AX1" s="2" t="inlineStr">
-        <is>
-          <t>1995</t>
-        </is>
-      </c>
-      <c r="AY1" s="2" t="inlineStr">
-        <is>
-          <t>1996</t>
-        </is>
-      </c>
-      <c r="AZ1" s="2" t="inlineStr">
-        <is>
-          <t>1997</t>
-        </is>
-      </c>
-      <c r="BA1" s="2" t="inlineStr">
-        <is>
-          <t>1998</t>
-        </is>
-      </c>
-      <c r="BB1" s="2" t="inlineStr">
-        <is>
-          <t>1999</t>
-        </is>
-      </c>
-      <c r="BC1" s="2" t="inlineStr">
-        <is>
-          <t>2000</t>
-        </is>
-      </c>
-      <c r="BD1" s="2" t="inlineStr">
-        <is>
-          <t>2001</t>
-        </is>
-      </c>
-      <c r="BE1" s="2" t="inlineStr">
-        <is>
-          <t>2002</t>
-        </is>
-      </c>
-      <c r="BF1" s="2" t="inlineStr">
-        <is>
-          <t>2003</t>
-        </is>
-      </c>
-      <c r="BG1" s="2" t="inlineStr">
-        <is>
-          <t>2004</t>
-        </is>
-      </c>
-      <c r="BH1" s="2" t="inlineStr">
-        <is>
-          <t>2005</t>
-        </is>
-      </c>
-      <c r="BI1" s="2" t="inlineStr">
-        <is>
-          <t>2006</t>
-        </is>
-      </c>
-      <c r="BJ1" s="2" t="inlineStr">
-        <is>
-          <t>2007</t>
-        </is>
-      </c>
-      <c r="BK1" s="2" t="inlineStr">
-        <is>
-          <t>2008</t>
-        </is>
-      </c>
-      <c r="BL1" s="2" t="inlineStr">
-        <is>
-          <t>2009</t>
-        </is>
-      </c>
-      <c r="BM1" s="2" t="inlineStr">
-        <is>
-          <t>2010</t>
-        </is>
-      </c>
-      <c r="BN1" s="2" t="inlineStr">
-        <is>
-          <t>2011</t>
-        </is>
-      </c>
-      <c r="BO1" s="2" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="BP1" s="2" t="inlineStr">
-        <is>
-          <t>2013</t>
-        </is>
-      </c>
-      <c r="BQ1" s="2" t="inlineStr">
-        <is>
-          <t>2014</t>
-        </is>
-      </c>
-      <c r="BR1" s="2" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-      <c r="BS1" s="2" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="BT1" s="2" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="BU1" s="2" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="BV1" s="2" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
+      <c r="E1" s="2" t="n">
+        <v>1950</v>
+      </c>
+      <c r="F1" s="2" t="n">
+        <v>1951</v>
+      </c>
+      <c r="G1" s="2" t="n">
+        <v>1952</v>
+      </c>
+      <c r="H1" s="2" t="n">
+        <v>1953</v>
+      </c>
+      <c r="I1" s="2" t="n">
+        <v>1954</v>
+      </c>
+      <c r="J1" s="2" t="n">
+        <v>1955</v>
+      </c>
+      <c r="K1" s="2" t="n">
+        <v>1956</v>
+      </c>
+      <c r="L1" s="2" t="n">
+        <v>1957</v>
+      </c>
+      <c r="M1" s="2" t="n">
+        <v>1958</v>
+      </c>
+      <c r="N1" s="2" t="n">
+        <v>1959</v>
+      </c>
+      <c r="O1" s="2" t="n">
+        <v>1960</v>
+      </c>
+      <c r="P1" s="2" t="n">
+        <v>1961</v>
+      </c>
+      <c r="Q1" s="2" t="n">
+        <v>1962</v>
+      </c>
+      <c r="R1" s="2" t="n">
+        <v>1963</v>
+      </c>
+      <c r="S1" s="2" t="n">
+        <v>1964</v>
+      </c>
+      <c r="T1" s="2" t="n">
+        <v>1965</v>
+      </c>
+      <c r="U1" s="2" t="n">
+        <v>1966</v>
+      </c>
+      <c r="V1" s="2" t="n">
+        <v>1967</v>
+      </c>
+      <c r="W1" s="2" t="n">
+        <v>1968</v>
+      </c>
+      <c r="X1" s="2" t="n">
+        <v>1969</v>
+      </c>
+      <c r="Y1" s="2" t="n">
+        <v>1970</v>
+      </c>
+      <c r="Z1" s="2" t="n">
+        <v>1971</v>
+      </c>
+      <c r="AA1" s="2" t="n">
+        <v>1972</v>
+      </c>
+      <c r="AB1" s="2" t="n">
+        <v>1973</v>
+      </c>
+      <c r="AC1" s="2" t="n">
+        <v>1974</v>
+      </c>
+      <c r="AD1" s="2" t="n">
+        <v>1975</v>
+      </c>
+      <c r="AE1" s="2" t="n">
+        <v>1976</v>
+      </c>
+      <c r="AF1" s="2" t="n">
+        <v>1977</v>
+      </c>
+      <c r="AG1" s="2" t="n">
+        <v>1978</v>
+      </c>
+      <c r="AH1" s="2" t="n">
+        <v>1979</v>
+      </c>
+      <c r="AI1" s="2" t="n">
+        <v>1980</v>
+      </c>
+      <c r="AJ1" s="2" t="n">
+        <v>1981</v>
+      </c>
+      <c r="AK1" s="2" t="n">
+        <v>1982</v>
+      </c>
+      <c r="AL1" s="2" t="n">
+        <v>1983</v>
+      </c>
+      <c r="AM1" s="2" t="n">
+        <v>1984</v>
+      </c>
+      <c r="AN1" s="2" t="n">
+        <v>1985</v>
+      </c>
+      <c r="AO1" s="2" t="n">
+        <v>1986</v>
+      </c>
+      <c r="AP1" s="2" t="n">
+        <v>1987</v>
+      </c>
+      <c r="AQ1" s="2" t="n">
+        <v>1988</v>
+      </c>
+      <c r="AR1" s="2" t="n">
+        <v>1989</v>
+      </c>
+      <c r="AS1" s="2" t="n">
+        <v>1990</v>
+      </c>
+      <c r="AT1" s="2" t="n">
+        <v>1991</v>
+      </c>
+      <c r="AU1" s="2" t="n">
+        <v>1992</v>
+      </c>
+      <c r="AV1" s="2" t="n">
+        <v>1993</v>
+      </c>
+      <c r="AW1" s="2" t="n">
+        <v>1994</v>
+      </c>
+      <c r="AX1" s="2" t="n">
+        <v>1995</v>
+      </c>
+      <c r="AY1" s="2" t="n">
+        <v>1996</v>
+      </c>
+      <c r="AZ1" s="2" t="n">
+        <v>1997</v>
+      </c>
+      <c r="BA1" s="2" t="n">
+        <v>1998</v>
+      </c>
+      <c r="BB1" s="2" t="n">
+        <v>1999</v>
+      </c>
+      <c r="BC1" s="2" t="n">
+        <v>2000</v>
+      </c>
+      <c r="BD1" s="2" t="n">
+        <v>2001</v>
+      </c>
+      <c r="BE1" s="2" t="n">
+        <v>2002</v>
+      </c>
+      <c r="BF1" s="2" t="n">
+        <v>2003</v>
+      </c>
+      <c r="BG1" s="2" t="n">
+        <v>2004</v>
+      </c>
+      <c r="BH1" s="2" t="n">
+        <v>2005</v>
+      </c>
+      <c r="BI1" s="2" t="n">
+        <v>2006</v>
+      </c>
+      <c r="BJ1" s="2" t="n">
+        <v>2007</v>
+      </c>
+      <c r="BK1" s="2" t="n">
+        <v>2008</v>
+      </c>
+      <c r="BL1" s="2" t="n">
+        <v>2009</v>
+      </c>
+      <c r="BM1" s="2" t="n">
+        <v>2010</v>
+      </c>
+      <c r="BN1" s="2" t="n">
+        <v>2011</v>
+      </c>
+      <c r="BO1" s="2" t="n">
+        <v>2012</v>
+      </c>
+      <c r="BP1" s="2" t="n">
+        <v>2013</v>
+      </c>
+      <c r="BQ1" s="2" t="n">
+        <v>2014</v>
+      </c>
+      <c r="BR1" s="2" t="n">
+        <v>2015</v>
+      </c>
+      <c r="BS1" s="2" t="n">
+        <v>2016</v>
+      </c>
+      <c r="BT1" s="2" t="n">
+        <v>2017</v>
+      </c>
+      <c r="BU1" s="2" t="n">
+        <v>2018</v>
+      </c>
+      <c r="BV1" s="2" t="n">
+        <v>2019</v>
       </c>
     </row>
     <row r="2">
@@ -40393,6 +40304,245 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Group SPPR: all</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>All basal sources, including imports. Models are separate. Blank means unavailable, not zero.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>group_name</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>No extracted model is available for this ecosystem.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Group SPPR: inner</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>Internal sources: primary producers and detritus; excludes imports. Models are separate. Blank means unavailable, not zero.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>group_name</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>No extracted model is available for this ecosystem.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Group SPPR: PP</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>Primary producers only; excludes detritus and imports. Models are separate. Blank means unavailable, not zero.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>group_name</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>No extracted model is available for this ecosystem.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="90" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Recycling diagnostics from diagnose_sppr()</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>b: detrital recycling; rho living: living food-web cycles. Each must be below 1 for convergence; these are necessary, not sufficient checks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>TE_option</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>rho living</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>diagnostic status</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>b converges</t>
+        </is>
+      </c>
+      <c r="G4" s="7" t="inlineStr">
+        <is>
+          <t>living converges</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
+          <t>input balanced</t>
+        </is>
+      </c>
+      <c r="I4" s="7" t="inlineStr">
+        <is>
+          <t>configuration</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -40571,355 +40721,215 @@
           <t>trophic_level</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>1950</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>1951</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>1952</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>1953</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>1954</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>1955</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>1956</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>1957</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>1958</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>1959</t>
-        </is>
-      </c>
-      <c r="M4" s="3" t="inlineStr">
-        <is>
-          <t>1960</t>
-        </is>
-      </c>
-      <c r="N4" s="3" t="inlineStr">
-        <is>
-          <t>1961</t>
-        </is>
-      </c>
-      <c r="O4" s="3" t="inlineStr">
-        <is>
-          <t>1962</t>
-        </is>
-      </c>
-      <c r="P4" s="3" t="inlineStr">
-        <is>
-          <t>1963</t>
-        </is>
-      </c>
-      <c r="Q4" s="3" t="inlineStr">
-        <is>
-          <t>1964</t>
-        </is>
-      </c>
-      <c r="R4" s="3" t="inlineStr">
-        <is>
-          <t>1965</t>
-        </is>
-      </c>
-      <c r="S4" s="3" t="inlineStr">
-        <is>
-          <t>1966</t>
-        </is>
-      </c>
-      <c r="T4" s="3" t="inlineStr">
-        <is>
-          <t>1967</t>
-        </is>
-      </c>
-      <c r="U4" s="3" t="inlineStr">
-        <is>
-          <t>1968</t>
-        </is>
-      </c>
-      <c r="V4" s="3" t="inlineStr">
-        <is>
-          <t>1969</t>
-        </is>
-      </c>
-      <c r="W4" s="3" t="inlineStr">
-        <is>
-          <t>1970</t>
-        </is>
-      </c>
-      <c r="X4" s="3" t="inlineStr">
-        <is>
-          <t>1971</t>
-        </is>
-      </c>
-      <c r="Y4" s="3" t="inlineStr">
-        <is>
-          <t>1972</t>
-        </is>
-      </c>
-      <c r="Z4" s="3" t="inlineStr">
-        <is>
-          <t>1973</t>
-        </is>
-      </c>
-      <c r="AA4" s="3" t="inlineStr">
-        <is>
-          <t>1974</t>
-        </is>
-      </c>
-      <c r="AB4" s="3" t="inlineStr">
-        <is>
-          <t>1975</t>
-        </is>
-      </c>
-      <c r="AC4" s="3" t="inlineStr">
-        <is>
-          <t>1976</t>
-        </is>
-      </c>
-      <c r="AD4" s="3" t="inlineStr">
-        <is>
-          <t>1977</t>
-        </is>
-      </c>
-      <c r="AE4" s="3" t="inlineStr">
-        <is>
-          <t>1978</t>
-        </is>
-      </c>
-      <c r="AF4" s="3" t="inlineStr">
-        <is>
-          <t>1979</t>
-        </is>
-      </c>
-      <c r="AG4" s="3" t="inlineStr">
-        <is>
-          <t>1980</t>
-        </is>
-      </c>
-      <c r="AH4" s="3" t="inlineStr">
-        <is>
-          <t>1981</t>
-        </is>
-      </c>
-      <c r="AI4" s="3" t="inlineStr">
-        <is>
-          <t>1982</t>
-        </is>
-      </c>
-      <c r="AJ4" s="3" t="inlineStr">
-        <is>
-          <t>1983</t>
-        </is>
-      </c>
-      <c r="AK4" s="3" t="inlineStr">
-        <is>
-          <t>1984</t>
-        </is>
-      </c>
-      <c r="AL4" s="3" t="inlineStr">
-        <is>
-          <t>1985</t>
-        </is>
-      </c>
-      <c r="AM4" s="3" t="inlineStr">
-        <is>
-          <t>1986</t>
-        </is>
-      </c>
-      <c r="AN4" s="3" t="inlineStr">
-        <is>
-          <t>1987</t>
-        </is>
-      </c>
-      <c r="AO4" s="3" t="inlineStr">
-        <is>
-          <t>1988</t>
-        </is>
-      </c>
-      <c r="AP4" s="3" t="inlineStr">
-        <is>
-          <t>1989</t>
-        </is>
-      </c>
-      <c r="AQ4" s="3" t="inlineStr">
-        <is>
-          <t>1990</t>
-        </is>
-      </c>
-      <c r="AR4" s="3" t="inlineStr">
-        <is>
-          <t>1991</t>
-        </is>
-      </c>
-      <c r="AS4" s="3" t="inlineStr">
-        <is>
-          <t>1992</t>
-        </is>
-      </c>
-      <c r="AT4" s="3" t="inlineStr">
-        <is>
-          <t>1993</t>
-        </is>
-      </c>
-      <c r="AU4" s="3" t="inlineStr">
-        <is>
-          <t>1994</t>
-        </is>
-      </c>
-      <c r="AV4" s="3" t="inlineStr">
-        <is>
-          <t>1995</t>
-        </is>
-      </c>
-      <c r="AW4" s="3" t="inlineStr">
-        <is>
-          <t>1996</t>
-        </is>
-      </c>
-      <c r="AX4" s="3" t="inlineStr">
-        <is>
-          <t>1997</t>
-        </is>
-      </c>
-      <c r="AY4" s="3" t="inlineStr">
-        <is>
-          <t>1998</t>
-        </is>
-      </c>
-      <c r="AZ4" s="3" t="inlineStr">
-        <is>
-          <t>1999</t>
-        </is>
-      </c>
-      <c r="BA4" s="3" t="inlineStr">
-        <is>
-          <t>2000</t>
-        </is>
-      </c>
-      <c r="BB4" s="3" t="inlineStr">
-        <is>
-          <t>2001</t>
-        </is>
-      </c>
-      <c r="BC4" s="3" t="inlineStr">
-        <is>
-          <t>2002</t>
-        </is>
-      </c>
-      <c r="BD4" s="3" t="inlineStr">
-        <is>
-          <t>2003</t>
-        </is>
-      </c>
-      <c r="BE4" s="3" t="inlineStr">
-        <is>
-          <t>2004</t>
-        </is>
-      </c>
-      <c r="BF4" s="3" t="inlineStr">
-        <is>
-          <t>2005</t>
-        </is>
-      </c>
-      <c r="BG4" s="3" t="inlineStr">
-        <is>
-          <t>2006</t>
-        </is>
-      </c>
-      <c r="BH4" s="3" t="inlineStr">
-        <is>
-          <t>2007</t>
-        </is>
-      </c>
-      <c r="BI4" s="3" t="inlineStr">
-        <is>
-          <t>2008</t>
-        </is>
-      </c>
-      <c r="BJ4" s="3" t="inlineStr">
-        <is>
-          <t>2009</t>
-        </is>
-      </c>
-      <c r="BK4" s="3" t="inlineStr">
-        <is>
-          <t>2010</t>
-        </is>
-      </c>
-      <c r="BL4" s="3" t="inlineStr">
-        <is>
-          <t>2011</t>
-        </is>
-      </c>
-      <c r="BM4" s="3" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="BN4" s="3" t="inlineStr">
-        <is>
-          <t>2013</t>
-        </is>
-      </c>
-      <c r="BO4" s="3" t="inlineStr">
-        <is>
-          <t>2014</t>
-        </is>
-      </c>
-      <c r="BP4" s="3" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-      <c r="BQ4" s="3" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="BR4" s="3" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="BS4" s="3" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="BT4" s="3" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
+      <c r="C4" s="3" t="n">
+        <v>1950</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>1951</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>1952</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>1953</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>1954</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>1955</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>1956</v>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v>1957</v>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>1958</v>
+      </c>
+      <c r="L4" s="3" t="n">
+        <v>1959</v>
+      </c>
+      <c r="M4" s="3" t="n">
+        <v>1960</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>1961</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>1962</v>
+      </c>
+      <c r="P4" s="3" t="n">
+        <v>1963</v>
+      </c>
+      <c r="Q4" s="3" t="n">
+        <v>1964</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>1965</v>
+      </c>
+      <c r="S4" s="3" t="n">
+        <v>1966</v>
+      </c>
+      <c r="T4" s="3" t="n">
+        <v>1967</v>
+      </c>
+      <c r="U4" s="3" t="n">
+        <v>1968</v>
+      </c>
+      <c r="V4" s="3" t="n">
+        <v>1969</v>
+      </c>
+      <c r="W4" s="3" t="n">
+        <v>1970</v>
+      </c>
+      <c r="X4" s="3" t="n">
+        <v>1971</v>
+      </c>
+      <c r="Y4" s="3" t="n">
+        <v>1972</v>
+      </c>
+      <c r="Z4" s="3" t="n">
+        <v>1973</v>
+      </c>
+      <c r="AA4" s="3" t="n">
+        <v>1974</v>
+      </c>
+      <c r="AB4" s="3" t="n">
+        <v>1975</v>
+      </c>
+      <c r="AC4" s="3" t="n">
+        <v>1976</v>
+      </c>
+      <c r="AD4" s="3" t="n">
+        <v>1977</v>
+      </c>
+      <c r="AE4" s="3" t="n">
+        <v>1978</v>
+      </c>
+      <c r="AF4" s="3" t="n">
+        <v>1979</v>
+      </c>
+      <c r="AG4" s="3" t="n">
+        <v>1980</v>
+      </c>
+      <c r="AH4" s="3" t="n">
+        <v>1981</v>
+      </c>
+      <c r="AI4" s="3" t="n">
+        <v>1982</v>
+      </c>
+      <c r="AJ4" s="3" t="n">
+        <v>1983</v>
+      </c>
+      <c r="AK4" s="3" t="n">
+        <v>1984</v>
+      </c>
+      <c r="AL4" s="3" t="n">
+        <v>1985</v>
+      </c>
+      <c r="AM4" s="3" t="n">
+        <v>1986</v>
+      </c>
+      <c r="AN4" s="3" t="n">
+        <v>1987</v>
+      </c>
+      <c r="AO4" s="3" t="n">
+        <v>1988</v>
+      </c>
+      <c r="AP4" s="3" t="n">
+        <v>1989</v>
+      </c>
+      <c r="AQ4" s="3" t="n">
+        <v>1990</v>
+      </c>
+      <c r="AR4" s="3" t="n">
+        <v>1991</v>
+      </c>
+      <c r="AS4" s="3" t="n">
+        <v>1992</v>
+      </c>
+      <c r="AT4" s="3" t="n">
+        <v>1993</v>
+      </c>
+      <c r="AU4" s="3" t="n">
+        <v>1994</v>
+      </c>
+      <c r="AV4" s="3" t="n">
+        <v>1995</v>
+      </c>
+      <c r="AW4" s="3" t="n">
+        <v>1996</v>
+      </c>
+      <c r="AX4" s="3" t="n">
+        <v>1997</v>
+      </c>
+      <c r="AY4" s="3" t="n">
+        <v>1998</v>
+      </c>
+      <c r="AZ4" s="3" t="n">
+        <v>1999</v>
+      </c>
+      <c r="BA4" s="3" t="n">
+        <v>2000</v>
+      </c>
+      <c r="BB4" s="3" t="n">
+        <v>2001</v>
+      </c>
+      <c r="BC4" s="3" t="n">
+        <v>2002</v>
+      </c>
+      <c r="BD4" s="3" t="n">
+        <v>2003</v>
+      </c>
+      <c r="BE4" s="3" t="n">
+        <v>2004</v>
+      </c>
+      <c r="BF4" s="3" t="n">
+        <v>2005</v>
+      </c>
+      <c r="BG4" s="3" t="n">
+        <v>2006</v>
+      </c>
+      <c r="BH4" s="3" t="n">
+        <v>2007</v>
+      </c>
+      <c r="BI4" s="3" t="n">
+        <v>2008</v>
+      </c>
+      <c r="BJ4" s="3" t="n">
+        <v>2009</v>
+      </c>
+      <c r="BK4" s="3" t="n">
+        <v>2010</v>
+      </c>
+      <c r="BL4" s="3" t="n">
+        <v>2011</v>
+      </c>
+      <c r="BM4" s="3" t="n">
+        <v>2012</v>
+      </c>
+      <c r="BN4" s="3" t="n">
+        <v>2013</v>
+      </c>
+      <c r="BO4" s="3" t="n">
+        <v>2014</v>
+      </c>
+      <c r="BP4" s="3" t="n">
+        <v>2015</v>
+      </c>
+      <c r="BQ4" s="3" t="n">
+        <v>2016</v>
+      </c>
+      <c r="BR4" s="3" t="n">
+        <v>2017</v>
+      </c>
+      <c r="BS4" s="3" t="n">
+        <v>2018</v>
+      </c>
+      <c r="BT4" s="3" t="n">
+        <v>2019</v>
       </c>
     </row>
     <row r="5">
@@ -61167,7 +61177,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/data/LME_008/LME_008.xlsx
+++ b/data/LME_008/LME_008.xlsx
@@ -9,15 +9,18 @@
   <sheets>
     <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Catch" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="SPPR" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="sppr_all" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="sppr_inner" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="sppr_PP" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Recycling" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="PPR" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="NPP" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Final mappings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="SPPR" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="sppr_all" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="sppr_inner" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="sppr_PP" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Recycling" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="PPR" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="NPP" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'NPP'!$A$3:$O$73</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -454,13 +457,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D85"/>
+  <dimension ref="A1:D86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -617,9 +620,6 @@
       <c r="C15" t="n">
         <v>345179957.669</v>
       </c>
-      <c r="D15" t="n">
-        <v>51.8547</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -631,9 +631,6 @@
       <c r="C16" t="n">
         <v>297671073.256</v>
       </c>
-      <c r="D16" t="n">
-        <v>44.7177</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -645,9 +642,6 @@
       <c r="C17" t="n">
         <v>395274102.396</v>
       </c>
-      <c r="D17" t="n">
-        <v>59.3801</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -659,9 +653,6 @@
       <c r="C18" t="n">
         <v>401227920.35</v>
       </c>
-      <c r="D18" t="n">
-        <v>60.2745</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -673,9 +664,6 @@
       <c r="C19" t="n">
         <v>560986351.207</v>
       </c>
-      <c r="D19" t="n">
-        <v>84.2743</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -687,9 +675,6 @@
       <c r="C20" t="n">
         <v>626279686.074</v>
       </c>
-      <c r="D20" t="n">
-        <v>94.083</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -701,9 +686,6 @@
       <c r="C21" t="n">
         <v>665084006.7130001</v>
       </c>
-      <c r="D21" t="n">
-        <v>99.91240000000001</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -715,9 +697,6 @@
       <c r="C22" t="n">
         <v>656136086.694</v>
       </c>
-      <c r="D22" t="n">
-        <v>98.5682</v>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -729,9 +708,6 @@
       <c r="C23" t="n">
         <v>549947814.477</v>
       </c>
-      <c r="D23" t="n">
-        <v>82.616</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -743,9 +719,6 @@
       <c r="C24" t="n">
         <v>621436636.198</v>
       </c>
-      <c r="D24" t="n">
-        <v>93.3554</v>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -757,9 +730,6 @@
       <c r="C25" t="n">
         <v>691608952.192</v>
       </c>
-      <c r="D25" t="n">
-        <v>103.8971</v>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -771,9 +741,6 @@
       <c r="C26" t="n">
         <v>781119914.531</v>
       </c>
-      <c r="D26" t="n">
-        <v>117.3439</v>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -785,9 +752,6 @@
       <c r="C27" t="n">
         <v>859774208.8329999</v>
       </c>
-      <c r="D27" t="n">
-        <v>129.1597</v>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -799,9 +763,6 @@
       <c r="C28" t="n">
         <v>1604840555.048</v>
       </c>
-      <c r="D28" t="n">
-        <v>241.0875</v>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -813,9 +774,6 @@
       <c r="C29" t="n">
         <v>1204635194.365</v>
       </c>
-      <c r="D29" t="n">
-        <v>180.9665</v>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -827,9 +785,6 @@
       <c r="C30" t="n">
         <v>1242806854.873</v>
       </c>
-      <c r="D30" t="n">
-        <v>186.7009</v>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -841,9 +796,6 @@
       <c r="C31" t="n">
         <v>927815976.5140001</v>
       </c>
-      <c r="D31" t="n">
-        <v>139.3813</v>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -855,9 +807,6 @@
       <c r="C32" t="n">
         <v>662039550.043</v>
       </c>
-      <c r="D32" t="n">
-        <v>99.455</v>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -869,9 +818,6 @@
       <c r="C33" t="n">
         <v>859020803.538</v>
       </c>
-      <c r="D33" t="n">
-        <v>129.0466</v>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -883,9 +829,6 @@
       <c r="C34" t="n">
         <v>875235031.368</v>
       </c>
-      <c r="D34" t="n">
-        <v>131.4823</v>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -897,9 +840,6 @@
       <c r="C35" t="n">
         <v>1346845892.899</v>
       </c>
-      <c r="D35" t="n">
-        <v>202.3302</v>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -911,9 +851,6 @@
       <c r="C36" t="n">
         <v>1172721106.567</v>
       </c>
-      <c r="D36" t="n">
-        <v>176.1722</v>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -925,9 +862,6 @@
       <c r="C37" t="n">
         <v>947703078.6569999</v>
       </c>
-      <c r="D37" t="n">
-        <v>142.3689</v>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -939,9 +873,6 @@
       <c r="C38" t="n">
         <v>1532566083.31</v>
       </c>
-      <c r="D38" t="n">
-        <v>230.23</v>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -953,9 +884,6 @@
       <c r="C39" t="n">
         <v>791522397.742</v>
       </c>
-      <c r="D39" t="n">
-        <v>118.9066</v>
-      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -967,9 +895,6 @@
       <c r="C40" t="n">
         <v>766445476.97</v>
       </c>
-      <c r="D40" t="n">
-        <v>115.1394</v>
-      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -981,9 +906,6 @@
       <c r="C41" t="n">
         <v>603946868.434</v>
       </c>
-      <c r="D41" t="n">
-        <v>90.72799999999999</v>
-      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -995,9 +917,6 @@
       <c r="C42" t="n">
         <v>349355754.453</v>
       </c>
-      <c r="D42" t="n">
-        <v>52.482</v>
-      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -1009,9 +928,6 @@
       <c r="C43" t="n">
         <v>398129864.232</v>
       </c>
-      <c r="D43" t="n">
-        <v>59.8091</v>
-      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -1023,9 +939,6 @@
       <c r="C44" t="n">
         <v>431773609.507</v>
       </c>
-      <c r="D44" t="n">
-        <v>64.8633</v>
-      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -1037,9 +950,6 @@
       <c r="C45" t="n">
         <v>431950123.476</v>
       </c>
-      <c r="D45" t="n">
-        <v>64.88979999999999</v>
-      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -1051,9 +961,6 @@
       <c r="C46" t="n">
         <v>456718672.419</v>
       </c>
-      <c r="D46" t="n">
-        <v>68.61060000000001</v>
-      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -1065,9 +972,6 @@
       <c r="C47" t="n">
         <v>445595756.733</v>
       </c>
-      <c r="D47" t="n">
-        <v>66.9397</v>
-      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -1079,9 +983,6 @@
       <c r="C48" t="n">
         <v>377064765.588</v>
       </c>
-      <c r="D48" t="n">
-        <v>56.6446</v>
-      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -1093,9 +994,6 @@
       <c r="C49" t="n">
         <v>456471677.769</v>
       </c>
-      <c r="D49" t="n">
-        <v>68.5735</v>
-      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -1107,9 +1005,6 @@
       <c r="C50" t="n">
         <v>481447438.292</v>
       </c>
-      <c r="D50" t="n">
-        <v>72.32550000000001</v>
-      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -1121,9 +1016,6 @@
       <c r="C51" t="n">
         <v>530110767.605</v>
       </c>
-      <c r="D51" t="n">
-        <v>79.636</v>
-      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -1135,9 +1027,6 @@
       <c r="C52" t="n">
         <v>449091976.679</v>
       </c>
-      <c r="D52" t="n">
-        <v>67.4649</v>
-      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -1149,9 +1038,6 @@
       <c r="C53" t="n">
         <v>482573452.172</v>
       </c>
-      <c r="D53" t="n">
-        <v>72.49469999999999</v>
-      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -1163,9 +1049,6 @@
       <c r="C54" t="n">
         <v>504508745.923</v>
       </c>
-      <c r="D54" t="n">
-        <v>75.7899</v>
-      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -1177,9 +1060,6 @@
       <c r="C55" t="n">
         <v>443975388.959</v>
       </c>
-      <c r="D55" t="n">
-        <v>66.69629999999999</v>
-      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -1191,9 +1071,6 @@
       <c r="C56" t="n">
         <v>391677998</v>
       </c>
-      <c r="D56" t="n">
-        <v>58.8399</v>
-      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -1205,9 +1082,6 @@
       <c r="C57" t="n">
         <v>324809053.574</v>
       </c>
-      <c r="D57" t="n">
-        <v>48.7945</v>
-      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -1219,9 +1093,6 @@
       <c r="C58" t="n">
         <v>228683711.26</v>
       </c>
-      <c r="D58" t="n">
-        <v>34.3541</v>
-      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -1233,9 +1104,6 @@
       <c r="C59" t="n">
         <v>154725681.26</v>
       </c>
-      <c r="D59" t="n">
-        <v>23.2437</v>
-      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -1247,9 +1115,6 @@
       <c r="C60" t="n">
         <v>136567766.098</v>
       </c>
-      <c r="D60" t="n">
-        <v>20.5159</v>
-      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -1261,9 +1126,6 @@
       <c r="C61" t="n">
         <v>130360664.833</v>
       </c>
-      <c r="D61" t="n">
-        <v>19.5835</v>
-      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -1275,9 +1137,6 @@
       <c r="C62" t="n">
         <v>141541470.33</v>
       </c>
-      <c r="D62" t="n">
-        <v>21.2631</v>
-      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -1290,7 +1149,7 @@
         <v>143149946.218</v>
       </c>
       <c r="D63" t="n">
-        <v>21.5047</v>
+        <v>19.2351</v>
       </c>
     </row>
     <row r="64">
@@ -1304,7 +1163,7 @@
         <v>146064001.255</v>
       </c>
       <c r="D64" t="n">
-        <v>21.9425</v>
+        <v>18.2872</v>
       </c>
     </row>
     <row r="65">
@@ -1318,7 +1177,7 @@
         <v>143929384.909</v>
       </c>
       <c r="D65" t="n">
-        <v>21.6218</v>
+        <v>18.7431</v>
       </c>
     </row>
     <row r="66">
@@ -1332,7 +1191,7 @@
         <v>149216500.134</v>
       </c>
       <c r="D66" t="n">
-        <v>22.4161</v>
+        <v>19.4222</v>
       </c>
     </row>
     <row r="67">
@@ -1346,7 +1205,7 @@
         <v>152886522.297</v>
       </c>
       <c r="D67" t="n">
-        <v>22.9674</v>
+        <v>19.6029</v>
       </c>
     </row>
     <row r="68">
@@ -1360,7 +1219,7 @@
         <v>131631444.562</v>
       </c>
       <c r="D68" t="n">
-        <v>19.7744</v>
+        <v>17.287</v>
       </c>
     </row>
     <row r="69">
@@ -1374,7 +1233,7 @@
         <v>143488976.546</v>
       </c>
       <c r="D69" t="n">
-        <v>21.5557</v>
+        <v>18.5383</v>
       </c>
     </row>
     <row r="70">
@@ -1388,7 +1247,7 @@
         <v>132800935.217</v>
       </c>
       <c r="D70" t="n">
-        <v>19.95</v>
+        <v>17.6139</v>
       </c>
     </row>
     <row r="71">
@@ -1402,7 +1261,7 @@
         <v>137897357.524</v>
       </c>
       <c r="D71" t="n">
-        <v>20.7157</v>
+        <v>16.5003</v>
       </c>
     </row>
     <row r="72">
@@ -1416,7 +1275,7 @@
         <v>132492765.435</v>
       </c>
       <c r="D72" t="n">
-        <v>19.9037</v>
+        <v>16.5981</v>
       </c>
     </row>
     <row r="73">
@@ -1430,7 +1289,7 @@
         <v>129439124.776</v>
       </c>
       <c r="D73" t="n">
-        <v>19.445</v>
+        <v>16.666</v>
       </c>
     </row>
     <row r="74">
@@ -1444,7 +1303,7 @@
         <v>127106994.123</v>
       </c>
       <c r="D74" t="n">
-        <v>19.0947</v>
+        <v>15.469</v>
       </c>
     </row>
     <row r="75">
@@ -1458,7 +1317,7 @@
         <v>127945190.884</v>
       </c>
       <c r="D75" t="n">
-        <v>19.2206</v>
+        <v>15.808</v>
       </c>
     </row>
     <row r="76">
@@ -1472,7 +1331,7 @@
         <v>104644625.857</v>
       </c>
       <c r="D76" t="n">
-        <v>15.7203</v>
+        <v>12.9576</v>
       </c>
     </row>
     <row r="77">
@@ -1486,7 +1345,7 @@
         <v>126687471.483</v>
       </c>
       <c r="D77" t="n">
-        <v>19.0316</v>
+        <v>16.2601</v>
       </c>
     </row>
     <row r="78">
@@ -1500,7 +1359,7 @@
         <v>126654210.666</v>
       </c>
       <c r="D78" t="n">
-        <v>19.0267</v>
+        <v>16.1935</v>
       </c>
     </row>
     <row r="79">
@@ -1514,7 +1373,7 @@
         <v>118975599.784</v>
       </c>
       <c r="D79" t="n">
-        <v>17.8731</v>
+        <v>15.037</v>
       </c>
     </row>
     <row r="80">
@@ -1528,7 +1387,7 @@
         <v>124438119.884</v>
       </c>
       <c r="D80" t="n">
-        <v>18.6937</v>
+        <v>16.4576</v>
       </c>
     </row>
     <row r="81">
@@ -1542,7 +1401,7 @@
         <v>119195190.57</v>
       </c>
       <c r="D81" t="n">
-        <v>17.9061</v>
+        <v>15.637</v>
       </c>
     </row>
     <row r="82">
@@ -1556,7 +1415,7 @@
         <v>69000049.059</v>
       </c>
       <c r="D82" t="n">
-        <v>10.3655</v>
+        <v>8.257899999999999</v>
       </c>
     </row>
     <row r="83">
@@ -1570,7 +1429,7 @@
         <v>86145416.802</v>
       </c>
       <c r="D83" t="n">
-        <v>12.9412</v>
+        <v>11.4378</v>
       </c>
     </row>
     <row r="84">
@@ -1584,17 +1443,2281 @@
         <v>75212513.43099999</v>
       </c>
       <c r="D84" t="n">
-        <v>11.2988</v>
+        <v>9.4552</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>PPR/NPP converts wet-weight PP to carbon at 9:1; NPP is the fixed 2019 ensemble median.</t>
+          <t>PPR/NPP converts wet-weight PP to carbon at 9:1 and uses the matching year's NPP ensemble median.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>PPR/NPP is blank for years without NPP; see NPP for availability and provenance.</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O73"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="6" max="6"/>
+    <col width="23" customWidth="1" min="7" max="7"/>
+    <col width="23" customWidth="1" min="8" max="8"/>
+    <col width="23" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="60" customWidth="1" min="11" max="11"/>
+    <col width="75" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="36" customWidth="1" min="14" max="14"/>
+    <col width="65" customWidth="1" min="15" max="15"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Annual net primary production, tonnes carbon per year</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>PPR/NPP uses the ensemble median for the matching catch year. Blank values are unavailable; no year is substituted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="32" customHeight="1">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>year</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>npp_antoinemorel_tC_yr</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>npp_vgpm_tC_yr</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>npp_eppley_tC_yr</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>npp_cbpm_tC_yr</t>
+        </is>
+      </c>
+      <c r="F3" s="7" t="inlineStr">
+        <is>
+          <t>npp_cafe_tC_yr</t>
+        </is>
+      </c>
+      <c r="G3" s="7" t="inlineStr">
+        <is>
+          <t>ens_median_tC_yr</t>
+        </is>
+      </c>
+      <c r="H3" s="7" t="inlineStr">
+        <is>
+          <t>ens_min_tC_yr</t>
+        </is>
+      </c>
+      <c r="I3" s="7" t="inlineStr">
+        <is>
+          <t>ens_max_tC_yr</t>
+        </is>
+      </c>
+      <c r="J3" s="7" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="K3" s="7" t="inlineStr">
+        <is>
+          <t>reason</t>
+        </is>
+      </c>
+      <c r="L3" s="7" t="inlineStr">
+        <is>
+          <t>provenance</t>
+        </is>
+      </c>
+      <c r="M3" s="7" t="inlineStr">
+        <is>
+          <t>n_models</t>
+        </is>
+      </c>
+      <c r="N3" s="7" t="inlineStr">
+        <is>
+          <t>available_models</t>
+        </is>
+      </c>
+      <c r="O3" s="7" t="inlineStr">
+        <is>
+          <t>ensemble_basis</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1950</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1951</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1952</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1953</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1954</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1955</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1956</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>1957</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1958</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>1959</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>1960</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>1961</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>1962</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>1963</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>1964</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>1965</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>1966</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>1967</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>1968</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1969</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>1970</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>1971</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>1972</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>1973</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>1974</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>1975</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>1976</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>1977</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>1978</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>1979</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>1980</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>1981</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>1982</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>1983</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>1984</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>1985</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>1986</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>1987</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>1988</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>1989</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>1990</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>1991</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>1992</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>1993</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>1994</v>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>1995</v>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>1996</v>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>1997</v>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="n">
+        <v>0</v>
+      </c>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>1998</v>
+      </c>
+      <c r="B52" t="n">
+        <v>82690345.81695017</v>
+      </c>
+      <c r="G52" t="n">
+        <v>82690345.81695017</v>
+      </c>
+      <c r="H52" t="n">
+        <v>82690345.81695017</v>
+      </c>
+      <c r="I52" t="n">
+        <v>82690345.81695017</v>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>vgpm: unsupported_year; eppley: unsupported_year; cbpm: unsupported_year; cafe: unsupported_year</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/1998/65dfd93f461846d2/provenance.json</t>
+        </is>
+      </c>
+      <c r="M52" t="n">
+        <v>1</v>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>antoinemorel</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>1999</v>
+      </c>
+      <c r="B53" t="n">
+        <v>88746842.83172545</v>
+      </c>
+      <c r="G53" t="n">
+        <v>88746842.83172545</v>
+      </c>
+      <c r="H53" t="n">
+        <v>88746842.83172545</v>
+      </c>
+      <c r="I53" t="n">
+        <v>88746842.83172545</v>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>vgpm: unsupported_year; eppley: unsupported_year; cbpm: unsupported_year; cafe: unsupported_year</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/1999/4b1cb2d6cba203fb/provenance.json</t>
+        </is>
+      </c>
+      <c r="M53" t="n">
+        <v>1</v>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>antoinemorel</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>2000</v>
+      </c>
+      <c r="B54" t="n">
+        <v>85323040.88958755</v>
+      </c>
+      <c r="G54" t="n">
+        <v>85323040.88958755</v>
+      </c>
+      <c r="H54" t="n">
+        <v>85323040.88958755</v>
+      </c>
+      <c r="I54" t="n">
+        <v>85323040.88958755</v>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>vgpm: unsupported_year; eppley: unsupported_year; cbpm: unsupported_year; cafe: unsupported_year</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2000/4bea86f4cd09bd55/provenance.json</t>
+        </is>
+      </c>
+      <c r="M54" t="n">
+        <v>1</v>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>antoinemorel</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>2001</v>
+      </c>
+      <c r="B55" t="n">
+        <v>85364443.71076572</v>
+      </c>
+      <c r="G55" t="n">
+        <v>85364443.71076572</v>
+      </c>
+      <c r="H55" t="n">
+        <v>85364443.71076572</v>
+      </c>
+      <c r="I55" t="n">
+        <v>85364443.71076572</v>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>vgpm: unsupported_year; eppley: unsupported_year; cbpm: unsupported_year; cafe: unsupported_year</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2001/0ec8617947fb90b9/provenance.json</t>
+        </is>
+      </c>
+      <c r="M55" t="n">
+        <v>1</v>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>antoinemorel</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>2002</v>
+      </c>
+      <c r="B56" t="n">
+        <v>86657751.00941931</v>
+      </c>
+      <c r="G56" t="n">
+        <v>86657751.00941931</v>
+      </c>
+      <c r="H56" t="n">
+        <v>86657751.00941931</v>
+      </c>
+      <c r="I56" t="n">
+        <v>86657751.00941931</v>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>vgpm: unsupported_year; eppley: unsupported_year; cbpm: unsupported_year; cafe: unsupported_year</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2002/3789d747c9365882/provenance.json</t>
+        </is>
+      </c>
+      <c r="M56" t="n">
+        <v>1</v>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>antoinemorel</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>2003</v>
+      </c>
+      <c r="B57" t="n">
+        <v>84605417.57447094</v>
+      </c>
+      <c r="C57" t="n">
+        <v>100611188.7088613</v>
+      </c>
+      <c r="D57" t="n">
+        <v>72731314.06198271</v>
+      </c>
+      <c r="E57" t="n">
+        <v>104037110.5817032</v>
+      </c>
+      <c r="F57" t="n">
+        <v>63289046.71466728</v>
+      </c>
+      <c r="G57" t="n">
+        <v>84605417.57447094</v>
+      </c>
+      <c r="H57" t="n">
+        <v>63289046.71466728</v>
+      </c>
+      <c r="I57" t="n">
+        <v>104037110.5817032</v>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2003/c3a820791e3378ef/provenance.json</t>
+        </is>
+      </c>
+      <c r="M57" t="n">
+        <v>5</v>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>2004</v>
+      </c>
+      <c r="B58" t="n">
+        <v>86001404.56537944</v>
+      </c>
+      <c r="C58" t="n">
+        <v>100421624.133664</v>
+      </c>
+      <c r="D58" t="n">
+        <v>73238812.31660342</v>
+      </c>
+      <c r="E58" t="n">
+        <v>100506303.9001593</v>
+      </c>
+      <c r="F58" t="n">
+        <v>59337735.94397444</v>
+      </c>
+      <c r="G58" t="n">
+        <v>86001404.56537944</v>
+      </c>
+      <c r="H58" t="n">
+        <v>59337735.94397444</v>
+      </c>
+      <c r="I58" t="n">
+        <v>100506303.9001593</v>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2004/f4cd3b4c7fc3dd8b/provenance.json</t>
+        </is>
+      </c>
+      <c r="M58" t="n">
+        <v>5</v>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>2005</v>
+      </c>
+      <c r="B59" t="n">
+        <v>83772831.89159907</v>
+      </c>
+      <c r="C59" t="n">
+        <v>103180369.4266318</v>
+      </c>
+      <c r="D59" t="n">
+        <v>74184524.61710005</v>
+      </c>
+      <c r="E59" t="n">
+        <v>102859182.6511817</v>
+      </c>
+      <c r="F59" t="n">
+        <v>60175031.96468047</v>
+      </c>
+      <c r="G59" t="n">
+        <v>83772831.89159907</v>
+      </c>
+      <c r="H59" t="n">
+        <v>60175031.96468047</v>
+      </c>
+      <c r="I59" t="n">
+        <v>103180369.4266318</v>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2005/4bdcca026379c2bd/provenance.json</t>
+        </is>
+      </c>
+      <c r="M59" t="n">
+        <v>5</v>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>2006</v>
+      </c>
+      <c r="B60" t="n">
+        <v>92858461.09247842</v>
+      </c>
+      <c r="C60" t="n">
+        <v>111466873.0022741</v>
+      </c>
+      <c r="D60" t="n">
+        <v>80174575.04253708</v>
+      </c>
+      <c r="E60" t="n">
+        <v>103343880.8989386</v>
+      </c>
+      <c r="F60" t="n">
+        <v>61253685.74582056</v>
+      </c>
+      <c r="G60" t="n">
+        <v>92858461.09247842</v>
+      </c>
+      <c r="H60" t="n">
+        <v>61253685.74582056</v>
+      </c>
+      <c r="I60" t="n">
+        <v>111466873.0022741</v>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2006/3ea13e28f3d7c994/provenance.json</t>
+        </is>
+      </c>
+      <c r="M60" t="n">
+        <v>5</v>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>2007</v>
+      </c>
+      <c r="B61" t="n">
+        <v>88693530.09972911</v>
+      </c>
+      <c r="C61" t="n">
+        <v>99561412.35306004</v>
+      </c>
+      <c r="D61" t="n">
+        <v>73013222.34086682</v>
+      </c>
+      <c r="E61" t="n">
+        <v>100839816.7870956</v>
+      </c>
+      <c r="F61" t="n">
+        <v>63881953.41156948</v>
+      </c>
+      <c r="G61" t="n">
+        <v>88693530.09972911</v>
+      </c>
+      <c r="H61" t="n">
+        <v>63881953.41156948</v>
+      </c>
+      <c r="I61" t="n">
+        <v>100839816.7870956</v>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2007/af2057f32254ca19/provenance.json</t>
+        </is>
+      </c>
+      <c r="M61" t="n">
+        <v>5</v>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>2008</v>
+      </c>
+      <c r="B62" t="n">
+        <v>86296399.40812966</v>
+      </c>
+      <c r="C62" t="n">
+        <v>105394467.7806241</v>
+      </c>
+      <c r="D62" t="n">
+        <v>75386164.18373506</v>
+      </c>
+      <c r="E62" t="n">
+        <v>100519515.6976681</v>
+      </c>
+      <c r="F62" t="n">
+        <v>64738650.0562477</v>
+      </c>
+      <c r="G62" t="n">
+        <v>86296399.40812966</v>
+      </c>
+      <c r="H62" t="n">
+        <v>64738650.0562477</v>
+      </c>
+      <c r="I62" t="n">
+        <v>105394467.7806241</v>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2008/51e4a448b1f4148f/provenance.json</t>
+        </is>
+      </c>
+      <c r="M62" t="n">
+        <v>5</v>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>2009</v>
+      </c>
+      <c r="B63" t="n">
+        <v>91299008.4189682</v>
+      </c>
+      <c r="C63" t="n">
+        <v>107522988.2904307</v>
+      </c>
+      <c r="D63" t="n">
+        <v>77450633.93115248</v>
+      </c>
+      <c r="E63" t="n">
+        <v>98464368.89561568</v>
+      </c>
+      <c r="F63" t="n">
+        <v>60987225.22186502</v>
+      </c>
+      <c r="G63" t="n">
+        <v>91299008.4189682</v>
+      </c>
+      <c r="H63" t="n">
+        <v>60987225.22186502</v>
+      </c>
+      <c r="I63" t="n">
+        <v>107522988.2904307</v>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2009/d16425bc4ac9cb7d/provenance.json</t>
+        </is>
+      </c>
+      <c r="M63" t="n">
+        <v>5</v>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>2010</v>
+      </c>
+      <c r="B64" t="n">
+        <v>89930145.2529154</v>
+      </c>
+      <c r="C64" t="n">
+        <v>104866037.9020123</v>
+      </c>
+      <c r="D64" t="n">
+        <v>76291727.95326811</v>
+      </c>
+      <c r="E64" t="n">
+        <v>108384660.3984948</v>
+      </c>
+      <c r="F64" t="n">
+        <v>58113705.70657526</v>
+      </c>
+      <c r="G64" t="n">
+        <v>89930145.2529154</v>
+      </c>
+      <c r="H64" t="n">
+        <v>58113705.70657526</v>
+      </c>
+      <c r="I64" t="n">
+        <v>108384660.3984948</v>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2010/5d2cc2c9685a81c9/provenance.json</t>
+        </is>
+      </c>
+      <c r="M64" t="n">
+        <v>5</v>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>2011</v>
+      </c>
+      <c r="B65" t="n">
+        <v>89732612.48365515</v>
+      </c>
+      <c r="C65" t="n">
+        <v>104036120.1652467</v>
+      </c>
+      <c r="D65" t="n">
+        <v>74613904.16851188</v>
+      </c>
+      <c r="E65" t="n">
+        <v>99675093.38323237</v>
+      </c>
+      <c r="F65" t="n">
+        <v>64200088.92930587</v>
+      </c>
+      <c r="G65" t="n">
+        <v>89732612.48365515</v>
+      </c>
+      <c r="H65" t="n">
+        <v>64200088.92930587</v>
+      </c>
+      <c r="I65" t="n">
+        <v>104036120.1652467</v>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2011/a6c24b780ceeb354/provenance.json</t>
+        </is>
+      </c>
+      <c r="M65" t="n">
+        <v>5</v>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>2012</v>
+      </c>
+      <c r="B66" t="n">
+        <v>86570038.98064388</v>
+      </c>
+      <c r="C66" t="n">
+        <v>106739097.1772659</v>
+      </c>
+      <c r="D66" t="n">
+        <v>77789694.68515775</v>
+      </c>
+      <c r="E66" t="n">
+        <v>101030827.9883351</v>
+      </c>
+      <c r="F66" t="n">
+        <v>59456519.22700091</v>
+      </c>
+      <c r="G66" t="n">
+        <v>86570038.98064388</v>
+      </c>
+      <c r="H66" t="n">
+        <v>59456519.22700091</v>
+      </c>
+      <c r="I66" t="n">
+        <v>106739097.1772659</v>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2012/2fd3c52e363d2259/provenance.json</t>
+        </is>
+      </c>
+      <c r="M66" t="n">
+        <v>5</v>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>2013</v>
+      </c>
+      <c r="B67" t="n">
+        <v>86903424.84468336</v>
+      </c>
+      <c r="C67" t="n">
+        <v>105339904.2589123</v>
+      </c>
+      <c r="D67" t="n">
+        <v>75763436.81860574</v>
+      </c>
+      <c r="E67" t="n">
+        <v>102164499.562402</v>
+      </c>
+      <c r="F67" t="n">
+        <v>57938017.95236631</v>
+      </c>
+      <c r="G67" t="n">
+        <v>86903424.84468336</v>
+      </c>
+      <c r="H67" t="n">
+        <v>57938017.95236631</v>
+      </c>
+      <c r="I67" t="n">
+        <v>105339904.2589123</v>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2013/821becabd572bab5/provenance.json</t>
+        </is>
+      </c>
+      <c r="M67" t="n">
+        <v>5</v>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>2014</v>
+      </c>
+      <c r="B68" t="n">
+        <v>87913193.81320225</v>
+      </c>
+      <c r="C68" t="n">
+        <v>109690868.1061597</v>
+      </c>
+      <c r="D68" t="n">
+        <v>79837963.57217988</v>
+      </c>
+      <c r="E68" t="n">
+        <v>98732441.11771654</v>
+      </c>
+      <c r="F68" t="n">
+        <v>65577375.93594625</v>
+      </c>
+      <c r="G68" t="n">
+        <v>87913193.81320225</v>
+      </c>
+      <c r="H68" t="n">
+        <v>65577375.93594625</v>
+      </c>
+      <c r="I68" t="n">
+        <v>109690868.1061597</v>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2014/c9d1725dde41256d/provenance.json</t>
+        </is>
+      </c>
+      <c r="M68" t="n">
+        <v>5</v>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B69" t="n">
+        <v>84012809.57673474</v>
+      </c>
+      <c r="C69" t="n">
+        <v>105272890.3852388</v>
+      </c>
+      <c r="D69" t="n">
+        <v>75608735.56788649</v>
+      </c>
+      <c r="E69" t="n">
+        <v>97312741.43811516</v>
+      </c>
+      <c r="F69" t="n">
+        <v>55254305.42422757</v>
+      </c>
+      <c r="G69" t="n">
+        <v>84012809.57673474</v>
+      </c>
+      <c r="H69" t="n">
+        <v>55254305.42422757</v>
+      </c>
+      <c r="I69" t="n">
+        <v>105272890.3852388</v>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2015/9d39afaaa8b014f8/provenance.json</t>
+        </is>
+      </c>
+      <c r="M69" t="n">
+        <v>5</v>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>2016</v>
+      </c>
+      <c r="B70" t="n">
+        <v>84695756.05470335</v>
+      </c>
+      <c r="C70" t="n">
+        <v>103028493.2294863</v>
+      </c>
+      <c r="D70" t="n">
+        <v>74480908.94858085</v>
+      </c>
+      <c r="E70" t="n">
+        <v>99965738.94650383</v>
+      </c>
+      <c r="F70" t="n">
+        <v>56140069.45055447</v>
+      </c>
+      <c r="G70" t="n">
+        <v>84695756.05470335</v>
+      </c>
+      <c r="H70" t="n">
+        <v>56140069.45055447</v>
+      </c>
+      <c r="I70" t="n">
+        <v>103028493.2294863</v>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2016/cfbe2d742214e408/provenance.json</t>
+        </is>
+      </c>
+      <c r="M70" t="n">
+        <v>5</v>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>2017</v>
+      </c>
+      <c r="B71" t="n">
+        <v>92840339.55278115</v>
+      </c>
+      <c r="C71" t="n">
+        <v>119608029.557969</v>
+      </c>
+      <c r="D71" t="n">
+        <v>86930158.36637032</v>
+      </c>
+      <c r="E71" t="n">
+        <v>98662938.03382713</v>
+      </c>
+      <c r="F71" t="n">
+        <v>58374602.79868849</v>
+      </c>
+      <c r="G71" t="n">
+        <v>92840339.55278115</v>
+      </c>
+      <c r="H71" t="n">
+        <v>58374602.79868849</v>
+      </c>
+      <c r="I71" t="n">
+        <v>119608029.557969</v>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2017/e85bc3c6652e1ebf/provenance.json</t>
+        </is>
+      </c>
+      <c r="M71" t="n">
+        <v>5</v>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B72" t="n">
+        <v>83685127.07791637</v>
+      </c>
+      <c r="C72" t="n">
+        <v>101109915.0610602</v>
+      </c>
+      <c r="D72" t="n">
+        <v>75382820.37718859</v>
+      </c>
+      <c r="E72" t="n">
+        <v>90375349.20072137</v>
+      </c>
+      <c r="F72" t="n">
+        <v>51177121.56521724</v>
+      </c>
+      <c r="G72" t="n">
+        <v>83685127.07791637</v>
+      </c>
+      <c r="H72" t="n">
+        <v>51177121.56521724</v>
+      </c>
+      <c r="I72" t="n">
+        <v>101109915.0610602</v>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2018/786b5184701484b9/provenance.json</t>
+        </is>
+      </c>
+      <c r="M72" t="n">
+        <v>5</v>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B73" t="n">
+        <v>88384461.77432857</v>
+      </c>
+      <c r="C73" t="n">
+        <v>112746110.4057162</v>
+      </c>
+      <c r="D73" t="n">
+        <v>83954863.19836949</v>
+      </c>
+      <c r="E73" t="n">
+        <v>104162419.2669232</v>
+      </c>
+      <c r="F73" t="n">
+        <v>53363262.2442897</v>
+      </c>
+      <c r="G73" t="n">
+        <v>88384461.77432857</v>
+      </c>
+      <c r="H73" t="n">
+        <v>53363262.2442897</v>
+      </c>
+      <c r="I73" t="n">
+        <v>112746110.4057162</v>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2019/e82a6f61f15e47c4/provenance.json</t>
+        </is>
+      </c>
+      <c r="M73" t="n">
+        <v>5</v>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:O73"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -39047,1254 +41170,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C99"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>Specific PPR for LME_008</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>No final mappings are available for this ecosystem.</t>
+        </is>
+      </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Simple method, applied per taxon: SPPR = (1/TE)^(TL-1), TE = 0.1</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>taxon</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>trophic_level</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>sppr_simple</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Morone saxatilis</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="C5" t="n">
-        <v>4466.835922</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Lamna nasus</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>4.57</v>
-      </c>
-      <c r="C6" t="n">
-        <v>3715.352291</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Myxine glutinosa</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>4.54</v>
-      </c>
-      <c r="C7" t="n">
-        <v>3467.368505</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Xiphias gladius</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>4.53</v>
-      </c>
-      <c r="C8" t="n">
-        <v>3388.441561</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Isurus paucus</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>4.51</v>
-      </c>
-      <c r="C9" t="n">
-        <v>3235.936569</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Salmo salar</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="C10" t="n">
-        <v>3162.27766</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Isurus oxyrinchus</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="C11" t="n">
-        <v>3162.27766</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Merluccius bilinearis</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>4.49</v>
-      </c>
-      <c r="C12" t="n">
-        <v>3090.295433</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Kajikia albida</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>4.49</v>
-      </c>
-      <c r="C13" t="n">
-        <v>3090.295433</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Sphyraena barracuda</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>4.49</v>
-      </c>
-      <c r="C14" t="n">
-        <v>3090.295433</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Thunnus thynnus</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="C15" t="n">
-        <v>2818.382931</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Thunnus albacares</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>4.41</v>
-      </c>
-      <c r="C16" t="n">
-        <v>2570.395783</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Salvelinus alpinus</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>4.39</v>
-      </c>
-      <c r="C17" t="n">
-        <v>2454.708916</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Reinhardtius hippoglossoides</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>4.38</v>
-      </c>
-      <c r="C18" t="n">
-        <v>2398.832919</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Squalus acanthias</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>4.37</v>
-      </c>
-      <c r="C19" t="n">
-        <v>2344.228815</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Prionace glauca</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="C20" t="n">
-        <v>2238.721139</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Pollachius virens</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>4.31</v>
-      </c>
-      <c r="C21" t="n">
-        <v>2041.737945</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Thunnus alalunga</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="C22" t="n">
-        <v>1995.262315</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Urophycis tenuis</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>4.27</v>
-      </c>
-      <c r="C23" t="n">
-        <v>1862.087137</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Merluccius</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>4.27</v>
-      </c>
-      <c r="C24" t="n">
-        <v>1862.087137</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Scombridae</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>4.26</v>
-      </c>
-      <c r="C25" t="n">
-        <v>1819.700859</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Zoarces americanus</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>4.24</v>
-      </c>
-      <c r="C26" t="n">
-        <v>1737.800829</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Squalus</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>4.23</v>
-      </c>
-      <c r="C27" t="n">
-        <v>1698.243652</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Scombroidei</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="C28" t="n">
-        <v>1584.893192</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Teuthida</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>4.13</v>
-      </c>
-      <c r="C29" t="n">
-        <v>1348.962883</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Salvelinus</t>
-        </is>
-      </c>
-      <c r="B30" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="C30" t="n">
-        <v>1258.925412</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Gadus morhua</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
-        <v>4.09</v>
-      </c>
-      <c r="C31" t="n">
-        <v>1230.268771</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Hippoglossoides platessoides</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
-        <v>4.08</v>
-      </c>
-      <c r="C32" t="n">
-        <v>1202.264435</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Elasmobranchii</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="C33" t="n">
-        <v>1122.018454</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Sebastes norvegicus</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
-        <v>4.04</v>
-      </c>
-      <c r="C34" t="n">
-        <v>1096.478196</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Melanogrammus aeglefinus</t>
-        </is>
-      </c>
-      <c r="B35" t="n">
-        <v>4.03</v>
-      </c>
-      <c r="C35" t="n">
-        <v>1071.519305</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Hippoglossus hippoglossus</t>
-        </is>
-      </c>
-      <c r="B36" t="n">
-        <v>4</v>
-      </c>
-      <c r="C36" t="n">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Salmo</t>
-        </is>
-      </c>
-      <c r="B37" t="n">
-        <v>4</v>
-      </c>
-      <c r="C37" t="n">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Illex illecebrosus</t>
-        </is>
-      </c>
-      <c r="B38" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="C38" t="n">
-        <v>954.992586</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Coryphaenoides</t>
-        </is>
-      </c>
-      <c r="B39" t="n">
-        <v>3.97</v>
-      </c>
-      <c r="C39" t="n">
-        <v>933.2543010000001</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Brosme brosme</t>
-        </is>
-      </c>
-      <c r="B40" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="C40" t="n">
-        <v>794.3282349999999</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Cyclopterus lumpus</t>
-        </is>
-      </c>
-      <c r="B41" t="n">
-        <v>3.89</v>
-      </c>
-      <c r="C41" t="n">
-        <v>776.247117</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Anguilliformes</t>
-        </is>
-      </c>
-      <c r="B42" t="n">
-        <v>3.89</v>
-      </c>
-      <c r="C42" t="n">
-        <v>776.247117</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Centroscyllium fabricii</t>
-        </is>
-      </c>
-      <c r="B43" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="C43" t="n">
-        <v>691.830971</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Gadidae</t>
-        </is>
-      </c>
-      <c r="B44" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="C44" t="n">
-        <v>691.830971</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Anguilla rostrata</t>
-        </is>
-      </c>
-      <c r="B45" t="n">
-        <v>3.83</v>
-      </c>
-      <c r="C45" t="n">
-        <v>676.082975</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Rajidae</t>
-        </is>
-      </c>
-      <c r="B46" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="C46" t="n">
-        <v>660.693448</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Cottidae</t>
-        </is>
-      </c>
-      <c r="B47" t="n">
-        <v>3.81</v>
-      </c>
-      <c r="C47" t="n">
-        <v>645.654229</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Sebastes</t>
-        </is>
-      </c>
-      <c r="B48" t="n">
-        <v>3.79</v>
-      </c>
-      <c r="C48" t="n">
-        <v>616.595002</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Scorpaeniformes</t>
-        </is>
-      </c>
-      <c r="B49" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="C49" t="n">
-        <v>602.559586</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Anarhichas denticulatus</t>
-        </is>
-      </c>
-      <c r="B50" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="C50" t="n">
-        <v>562.341325</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Buccinum undatum</t>
-        </is>
-      </c>
-      <c r="B51" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="C51" t="n">
-        <v>562.341325</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Tautogolabrus adspersus</t>
-        </is>
-      </c>
-      <c r="B52" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="C52" t="n">
-        <v>524.80746</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Myoxocephalus</t>
-        </is>
-      </c>
-      <c r="B53" t="n">
-        <v>3.71</v>
-      </c>
-      <c r="C53" t="n">
-        <v>512.861384</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Homarus americanus</t>
-        </is>
-      </c>
-      <c r="B54" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="C54" t="n">
-        <v>501.187234</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Scomber scombrus</t>
-        </is>
-      </c>
-      <c r="B55" t="n">
-        <v>3.63</v>
-      </c>
-      <c r="C55" t="n">
-        <v>426.579519</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Pseudopleuronectes americanus</t>
-        </is>
-      </c>
-      <c r="B56" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="C56" t="n">
-        <v>416.869383</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Octopoda</t>
-        </is>
-      </c>
-      <c r="B57" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="C57" t="n">
-        <v>380.189396</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>Pleuronectiformes</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>3.57</v>
-      </c>
-      <c r="C58" t="n">
-        <v>371.535229</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>Anarhichas lupus</t>
-        </is>
-      </c>
-      <c r="B59" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="C59" t="n">
-        <v>354.813389</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>Chionoecetes opilio</t>
-        </is>
-      </c>
-      <c r="B60" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="C60" t="n">
-        <v>346.73685</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>Enchelyopus cimbrius</t>
-        </is>
-      </c>
-      <c r="B61" t="n">
-        <v>3.53</v>
-      </c>
-      <c r="C61" t="n">
-        <v>338.844156</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>Pleuronectidae</t>
-        </is>
-      </c>
-      <c r="B62" t="n">
-        <v>3.49</v>
-      </c>
-      <c r="C62" t="n">
-        <v>309.029543</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>Osmeridae</t>
-        </is>
-      </c>
-      <c r="B63" t="n">
-        <v>3.46</v>
-      </c>
-      <c r="C63" t="n">
-        <v>288.40315</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>Scyphozoa</t>
-        </is>
-      </c>
-      <c r="B64" t="n">
-        <v>3.46</v>
-      </c>
-      <c r="C64" t="n">
-        <v>288.40315</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>Myxinidae</t>
-        </is>
-      </c>
-      <c r="B65" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="C65" t="n">
-        <v>281.838293</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>Alosa pseudoharengus</t>
-        </is>
-      </c>
-      <c r="B66" t="n">
-        <v>3.39</v>
-      </c>
-      <c r="C66" t="n">
-        <v>245.470892</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>Clupea harengus</t>
-        </is>
-      </c>
-      <c r="B67" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="C67" t="n">
-        <v>239.883292</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>Anarhichas</t>
-        </is>
-      </c>
-      <c r="B68" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="C68" t="n">
-        <v>223.872114</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>Marine pelagic fishes not identified</t>
-        </is>
-      </c>
-      <c r="B69" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="C69" t="n">
-        <v>223.872114</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>Acipenser oxyrinchus</t>
-        </is>
-      </c>
-      <c r="B70" t="n">
-        <v>3.325</v>
-      </c>
-      <c r="C70" t="n">
-        <v>211.348904</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>Lycodes</t>
-        </is>
-      </c>
-      <c r="B71" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="C71" t="n">
-        <v>199.526231</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>Marine fishes not identified</t>
-        </is>
-      </c>
-      <c r="B72" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="C72" t="n">
-        <v>190.546072</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>Myzopsetta ferruginea</t>
-        </is>
-      </c>
-      <c r="B73" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="C73" t="n">
-        <v>190.546072</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>Marine groundfishes not identified</t>
-        </is>
-      </c>
-      <c r="B74" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="C74" t="n">
-        <v>165.958691</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Menidia menidia</t>
-        </is>
-      </c>
-      <c r="B75" t="n">
-        <v>3.19</v>
-      </c>
-      <c r="C75" t="n">
-        <v>154.881662</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>Glyptocephalus cynoglossus</t>
-        </is>
-      </c>
-      <c r="B76" t="n">
-        <v>3.17</v>
-      </c>
-      <c r="C76" t="n">
-        <v>147.910839</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>Clupeidae</t>
-        </is>
-      </c>
-      <c r="B77" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="C77" t="n">
-        <v>144.543977</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>Mallotus villosus</t>
-        </is>
-      </c>
-      <c r="B78" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="C78" t="n">
-        <v>141.253754</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Morone americana</t>
-        </is>
-      </c>
-      <c r="B79" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="C79" t="n">
-        <v>138.038426</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>Ammodytidae</t>
-        </is>
-      </c>
-      <c r="B80" t="n">
-        <v>3.11</v>
-      </c>
-      <c r="C80" t="n">
-        <v>128.824955</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>Busycon</t>
-        </is>
-      </c>
-      <c r="B81" t="n">
-        <v>3</v>
-      </c>
-      <c r="C81" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>Osmerus mordax</t>
-        </is>
-      </c>
-      <c r="B82" t="n">
-        <v>3</v>
-      </c>
-      <c r="C82" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Cancer irroratus</t>
-        </is>
-      </c>
-      <c r="B83" t="n">
-        <v>3</v>
-      </c>
-      <c r="C83" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Lithodidae</t>
-        </is>
-      </c>
-      <c r="B84" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="C84" t="n">
-        <v>66.069345</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Miscellaneous marine crustaceans</t>
-        </is>
-      </c>
-      <c r="B85" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="C85" t="n">
-        <v>50.118723</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Pandalus</t>
-        </is>
-      </c>
-      <c r="B86" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="C86" t="n">
-        <v>39.810717</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Brachyura</t>
-        </is>
-      </c>
-      <c r="B87" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="C87" t="n">
-        <v>39.810717</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Echinoidea</t>
-        </is>
-      </c>
-      <c r="B88" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="C88" t="n">
-        <v>32.359366</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Miscellaneous aquatic invertebrates</t>
-        </is>
-      </c>
-      <c r="B89" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="C89" t="n">
-        <v>26.915348</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>Strongylocentrotus droebachiensis</t>
-        </is>
-      </c>
-      <c r="B90" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="C90" t="n">
-        <v>19.952623</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Chionoecetes</t>
-        </is>
-      </c>
-      <c r="B91" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="C91" t="n">
-        <v>19.952623</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Bivalvia</t>
-        </is>
-      </c>
-      <c r="B92" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="C92" t="n">
-        <v>16.982437</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Mollusca</t>
-        </is>
-      </c>
-      <c r="B93" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="C93" t="n">
-        <v>12.589254</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Strongylocentrotus</t>
-        </is>
-      </c>
-      <c r="B94" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="C94" t="n">
-        <v>12.589254</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Placopecten magellanicus</t>
-        </is>
-      </c>
-      <c r="B95" t="n">
-        <v>2</v>
-      </c>
-      <c r="C95" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>Crassostrea virginica</t>
-        </is>
-      </c>
-      <c r="B96" t="n">
-        <v>2</v>
-      </c>
-      <c r="C96" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>No Ecopath model has been extracted for this ecosystem yet,</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>so the network-based SPPR methods are not available here.</t>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Models without a recorded mapping are not assigned invented taxon groups or weights.</t>
         </is>
       </c>
     </row>
@@ -40309,43 +41201,1254 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:C99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>Group SPPR: all</t>
-        </is>
-      </c>
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Specific PPR for LME_008</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
     </row>
-    <row r="2" ht="32" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>All basal sources, including imports. Models are separate. Blank means unavailable, not zero.</t>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Simple method, applied per taxon: SPPR = (1/TE)^(TL-1), TE = 0.1</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="32" customHeight="1">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>model</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>group_name</t>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>taxon</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>trophic_level</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>sppr_simple</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>No extracted model is available for this ecosystem.</t>
+          <t>Morone saxatilis</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="C5" t="n">
+        <v>4466.835922</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Lamna nasus</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="C6" t="n">
+        <v>3715.352291</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Myxine glutinosa</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>4.54</v>
+      </c>
+      <c r="C7" t="n">
+        <v>3467.368505</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Xiphias gladius</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="C8" t="n">
+        <v>3388.441561</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Isurus paucus</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>4.51</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3235.936569</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Salmo salar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="C10" t="n">
+        <v>3162.27766</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Isurus oxyrinchus</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="C11" t="n">
+        <v>3162.27766</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Merluccius bilinearis</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>4.49</v>
+      </c>
+      <c r="C12" t="n">
+        <v>3090.295433</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Kajikia albida</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>4.49</v>
+      </c>
+      <c r="C13" t="n">
+        <v>3090.295433</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Sphyraena barracuda</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>4.49</v>
+      </c>
+      <c r="C14" t="n">
+        <v>3090.295433</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Thunnus thynnus</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="C15" t="n">
+        <v>2818.382931</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Thunnus albacares</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>4.41</v>
+      </c>
+      <c r="C16" t="n">
+        <v>2570.395783</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Salvelinus alpinus</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="C17" t="n">
+        <v>2454.708916</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Reinhardtius hippoglossoides</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="C18" t="n">
+        <v>2398.832919</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Squalus acanthias</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>4.37</v>
+      </c>
+      <c r="C19" t="n">
+        <v>2344.228815</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Prionace glauca</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="C20" t="n">
+        <v>2238.721139</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Pollachius virens</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>4.31</v>
+      </c>
+      <c r="C21" t="n">
+        <v>2041.737945</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Thunnus alalunga</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1995.262315</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Urophycis tenuis</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>4.27</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1862.087137</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Merluccius</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>4.27</v>
+      </c>
+      <c r="C24" t="n">
+        <v>1862.087137</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Scombridae</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="C25" t="n">
+        <v>1819.700859</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Zoarces americanus</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>4.24</v>
+      </c>
+      <c r="C26" t="n">
+        <v>1737.800829</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Squalus</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>4.23</v>
+      </c>
+      <c r="C27" t="n">
+        <v>1698.243652</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Scombroidei</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="C28" t="n">
+        <v>1584.893192</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Teuthida</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>4.13</v>
+      </c>
+      <c r="C29" t="n">
+        <v>1348.962883</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Salvelinus</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="C30" t="n">
+        <v>1258.925412</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Gadus morhua</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="C31" t="n">
+        <v>1230.268771</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Hippoglossoides platessoides</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="C32" t="n">
+        <v>1202.264435</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Elasmobranchii</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="C33" t="n">
+        <v>1122.018454</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Sebastes norvegicus</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="C34" t="n">
+        <v>1096.478196</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Melanogrammus aeglefinus</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="C35" t="n">
+        <v>1071.519305</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Hippoglossus hippoglossus</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>4</v>
+      </c>
+      <c r="C36" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Salmo</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>4</v>
+      </c>
+      <c r="C37" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Illex illecebrosus</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="C38" t="n">
+        <v>954.992586</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Coryphaenoides</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="C39" t="n">
+        <v>933.2543010000001</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Brosme brosme</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="C40" t="n">
+        <v>794.3282349999999</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Cyclopterus lumpus</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="C41" t="n">
+        <v>776.247117</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Anguilliformes</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="C42" t="n">
+        <v>776.247117</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Centroscyllium fabricii</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="C43" t="n">
+        <v>691.830971</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Gadidae</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="C44" t="n">
+        <v>691.830971</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Anguilla rostrata</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="C45" t="n">
+        <v>676.082975</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Rajidae</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="C46" t="n">
+        <v>660.693448</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Cottidae</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="C47" t="n">
+        <v>645.654229</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Sebastes</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="C48" t="n">
+        <v>616.595002</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Scorpaeniformes</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="C49" t="n">
+        <v>602.559586</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Anarhichas denticulatus</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="C50" t="n">
+        <v>562.341325</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Buccinum undatum</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="C51" t="n">
+        <v>562.341325</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Tautogolabrus adspersus</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="C52" t="n">
+        <v>524.80746</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Myoxocephalus</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="C53" t="n">
+        <v>512.861384</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Homarus americanus</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="C54" t="n">
+        <v>501.187234</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Scomber scombrus</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="C55" t="n">
+        <v>426.579519</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Pseudopleuronectes americanus</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="C56" t="n">
+        <v>416.869383</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Octopoda</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="C57" t="n">
+        <v>380.189396</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Pleuronectiformes</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="C58" t="n">
+        <v>371.535229</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Anarhichas lupus</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="C59" t="n">
+        <v>354.813389</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Chionoecetes opilio</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="C60" t="n">
+        <v>346.73685</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Enchelyopus cimbrius</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="C61" t="n">
+        <v>338.844156</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Pleuronectidae</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="C62" t="n">
+        <v>309.029543</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Osmeridae</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="C63" t="n">
+        <v>288.40315</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Scyphozoa</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="C64" t="n">
+        <v>288.40315</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Myxinidae</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="C65" t="n">
+        <v>281.838293</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Alosa pseudoharengus</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="C66" t="n">
+        <v>245.470892</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Clupea harengus</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="C67" t="n">
+        <v>239.883292</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Anarhichas</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="C68" t="n">
+        <v>223.872114</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Marine pelagic fishes not identified</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="C69" t="n">
+        <v>223.872114</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Acipenser oxyrinchus</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>3.325</v>
+      </c>
+      <c r="C70" t="n">
+        <v>211.348904</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Lycodes</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="C71" t="n">
+        <v>199.526231</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Marine fishes not identified</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="C72" t="n">
+        <v>190.546072</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Myzopsetta ferruginea</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="C73" t="n">
+        <v>190.546072</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Marine groundfishes not identified</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="C74" t="n">
+        <v>165.958691</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Menidia menidia</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="C75" t="n">
+        <v>154.881662</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Glyptocephalus cynoglossus</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="C76" t="n">
+        <v>147.910839</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Clupeidae</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="C77" t="n">
+        <v>144.543977</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Mallotus villosus</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="C78" t="n">
+        <v>141.253754</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Morone americana</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="C79" t="n">
+        <v>138.038426</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Ammodytidae</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="C80" t="n">
+        <v>128.824955</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Busycon</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>3</v>
+      </c>
+      <c r="C81" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Osmerus mordax</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>3</v>
+      </c>
+      <c r="C82" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Cancer irroratus</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>3</v>
+      </c>
+      <c r="C83" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Lithodidae</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="C84" t="n">
+        <v>66.069345</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Miscellaneous marine crustaceans</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="C85" t="n">
+        <v>50.118723</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Pandalus</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="C86" t="n">
+        <v>39.810717</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Brachyura</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="C87" t="n">
+        <v>39.810717</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Echinoidea</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="C88" t="n">
+        <v>32.359366</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Miscellaneous aquatic invertebrates</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="C89" t="n">
+        <v>26.915348</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Strongylocentrotus droebachiensis</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="C90" t="n">
+        <v>19.952623</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Chionoecetes</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="C91" t="n">
+        <v>19.952623</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Bivalvia</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="C92" t="n">
+        <v>16.982437</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Mollusca</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="C93" t="n">
+        <v>12.589254</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Strongylocentrotus</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="C94" t="n">
+        <v>12.589254</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Placopecten magellanicus</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>2</v>
+      </c>
+      <c r="C95" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Crassostrea virginica</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>2</v>
+      </c>
+      <c r="C96" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>No Ecopath model has been extracted for this ecosystem yet,</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>so the network-based SPPR methods are not available here.</t>
         </is>
       </c>
     </row>
@@ -40370,14 +42473,14 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>Group SPPR: inner</t>
+          <t>Group SPPR: all</t>
         </is>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>Internal sources: primary producers and detritus; excludes imports. Models are separate. Blank means unavailable, not zero.</t>
+          <t>All basal sources, including imports. Models are separate. Blank means unavailable, not zero.</t>
         </is>
       </c>
     </row>
@@ -40421,14 +42524,14 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>Group SPPR: PP</t>
+          <t>Group SPPR: inner</t>
         </is>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>Primary producers only; excludes detritus and imports. Models are separate. Blank means unavailable, not zero.</t>
+          <t>Internal sources: primary producers and detritus; excludes imports. Models are separate. Blank means unavailable, not zero.</t>
         </is>
       </c>
     </row>
@@ -40457,6 +42560,57 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Group SPPR: PP</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>Primary producers only; excludes detritus and imports. Models are separate. Blank means unavailable, not zero.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>group_name</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>No extracted model is available for this ecosystem.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -40542,7 +42696,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -61175,132 +63329,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>Net primary production, 2019, tonnes carbon per year</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>satellite_model</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>npp_tC_yr</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Antoine-Morel</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>73963040.54786614</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>VGPM</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>94349673.77913333</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Eppley</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>70256205.96962364</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>CbPM</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>87166557.16560546</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>CAFE</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>44656142.60590772</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>ensemble median</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>73963040.54786614</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>ensemble min</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>44656142.60590772</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>ensemble max</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>94349673.77913333</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>water area (km2)</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>280726.9109772192</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>